--- a/nss_nominal_results.xlsx
+++ b/nss_nominal_results.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X314"/>
+  <dimension ref="A1:T314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,26 +533,6 @@
           <t>n_synth</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>tau1_actual</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>tau2_actual</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>tau1_ext</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>tau2_ext</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -617,18 +597,6 @@
       <c r="T2" t="n">
         <v>15</v>
       </c>
-      <c r="U2" t="n">
-        <v>0.5002182277490962</v>
-      </c>
-      <c r="V2" t="n">
-        <v>26.9094792834136</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.4995947567900242</v>
-      </c>
-      <c r="X2" t="n">
-        <v>26.81346415609186</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -693,18 +661,6 @@
       <c r="T3" t="n">
         <v>14</v>
       </c>
-      <c r="U3" t="n">
-        <v>0.4997976102629852</v>
-      </c>
-      <c r="V3" t="n">
-        <v>27.57381475751533</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.4997832169032367</v>
-      </c>
-      <c r="X3" t="n">
-        <v>28.06541495467351</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -769,18 +725,6 @@
       <c r="T4" t="n">
         <v>14</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.006801113286475</v>
-      </c>
-      <c r="V4" t="n">
-        <v>12.71448993346851</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.016922082121732</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12.32198140405657</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -845,18 +789,6 @@
       <c r="T5" t="n">
         <v>14</v>
       </c>
-      <c r="U5" t="n">
-        <v>2.016211267417882</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.176979862728773</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.016920801979281</v>
-      </c>
-      <c r="X5" t="n">
-        <v>5.197613151576792</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -921,18 +853,6 @@
       <c r="T6" t="n">
         <v>14</v>
       </c>
-      <c r="U6" t="n">
-        <v>2.066276242261012</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.90502422143684</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.086621011120573</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.805803097812817</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -997,18 +917,6 @@
       <c r="T7" t="n">
         <v>14</v>
       </c>
-      <c r="U7" t="n">
-        <v>2.034049597868921</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5.260963244190589</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.040333695910873</v>
-      </c>
-      <c r="X7" t="n">
-        <v>5.304445249695125</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1073,18 +981,6 @@
       <c r="T8" t="n">
         <v>14</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.967622679216896</v>
-      </c>
-      <c r="V8" t="n">
-        <v>5.064744680345135</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.958349671558221</v>
-      </c>
-      <c r="X8" t="n">
-        <v>5.023162685561245</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1149,18 +1045,6 @@
       <c r="T9" t="n">
         <v>14</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.999071008807392</v>
-      </c>
-      <c r="V9" t="n">
-        <v>11.30455992993102</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.010363129708649</v>
-      </c>
-      <c r="X9" t="n">
-        <v>4.998568108598027</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1225,18 +1109,6 @@
       <c r="T10" t="n">
         <v>14</v>
       </c>
-      <c r="U10" t="n">
-        <v>2.001354783774465</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.098743382345405</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.00278391444364</v>
-      </c>
-      <c r="X10" t="n">
-        <v>5.111745128368256</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1301,18 +1173,6 @@
       <c r="T11" t="n">
         <v>14</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.999857348355017</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.026165222459608</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.000168035200319</v>
-      </c>
-      <c r="X11" t="n">
-        <v>5.039082131781275</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1377,18 +1237,6 @@
       <c r="T12" t="n">
         <v>15</v>
       </c>
-      <c r="U12" t="n">
-        <v>5.998438471859546</v>
-      </c>
-      <c r="V12" t="n">
-        <v>15.28787564778972</v>
-      </c>
-      <c r="W12" t="n">
-        <v>5.97259049011994</v>
-      </c>
-      <c r="X12" t="n">
-        <v>15.41359811264274</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1453,18 +1301,6 @@
       <c r="T13" t="n">
         <v>15</v>
       </c>
-      <c r="U13" t="n">
-        <v>6.221778022395383</v>
-      </c>
-      <c r="V13" t="n">
-        <v>20.00831526593619</v>
-      </c>
-      <c r="W13" t="n">
-        <v>6.205520818216749</v>
-      </c>
-      <c r="X13" t="n">
-        <v>19.86979408234597</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1529,18 +1365,6 @@
       <c r="T14" t="n">
         <v>15</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.4978594056063652</v>
-      </c>
-      <c r="V14" t="n">
-        <v>12.35328944414173</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.497365694227858</v>
-      </c>
-      <c r="X14" t="n">
-        <v>10.59121395834416</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1605,18 +1429,6 @@
       <c r="T15" t="n">
         <v>15</v>
       </c>
-      <c r="U15" t="n">
-        <v>3.141279229980169</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.272734919082651</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.0994521644792</v>
-      </c>
-      <c r="X15" t="n">
-        <v>5.222155367235723</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1681,18 +1493,6 @@
       <c r="T16" t="n">
         <v>15</v>
       </c>
-      <c r="U16" t="n">
-        <v>3.728290955076979</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.205093473308176</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.474685296041848</v>
-      </c>
-      <c r="X16" t="n">
-        <v>7.269895440441693</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1757,18 +1557,6 @@
       <c r="T17" t="n">
         <v>14</v>
       </c>
-      <c r="U17" t="n">
-        <v>7.495617570223505</v>
-      </c>
-      <c r="V17" t="n">
-        <v>21.8478358546346</v>
-      </c>
-      <c r="W17" t="n">
-        <v>7.57682194532355</v>
-      </c>
-      <c r="X17" t="n">
-        <v>21.48739504696417</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1833,18 +1621,6 @@
       <c r="T18" t="n">
         <v>14</v>
       </c>
-      <c r="U18" t="n">
-        <v>5.109389325473416</v>
-      </c>
-      <c r="V18" t="n">
-        <v>49.99999999895654</v>
-      </c>
-      <c r="W18" t="n">
-        <v>5.321198514102854</v>
-      </c>
-      <c r="X18" t="n">
-        <v>14.67137722174738</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1909,18 +1685,6 @@
       <c r="T19" t="n">
         <v>14</v>
       </c>
-      <c r="U19" t="n">
-        <v>5.999491417296047</v>
-      </c>
-      <c r="V19" t="n">
-        <v>29.89361783175936</v>
-      </c>
-      <c r="W19" t="n">
-        <v>5.994725029940636</v>
-      </c>
-      <c r="X19" t="n">
-        <v>29.98559266382177</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1985,18 +1749,6 @@
       <c r="T20" t="n">
         <v>14</v>
       </c>
-      <c r="U20" t="n">
-        <v>7.223081111791313</v>
-      </c>
-      <c r="V20" t="n">
-        <v>22.28432553392026</v>
-      </c>
-      <c r="W20" t="n">
-        <v>7.084174627492986</v>
-      </c>
-      <c r="X20" t="n">
-        <v>21.38906808097333</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2061,18 +1813,6 @@
       <c r="T21" t="n">
         <v>14</v>
       </c>
-      <c r="U21" t="n">
-        <v>4.014971704847012</v>
-      </c>
-      <c r="V21" t="n">
-        <v>49.99878864120902</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.844918876132363</v>
-      </c>
-      <c r="X21" t="n">
-        <v>44.44904019380698</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2137,18 +1877,6 @@
       <c r="T22" t="n">
         <v>14</v>
       </c>
-      <c r="U22" t="n">
-        <v>6.917046222075513</v>
-      </c>
-      <c r="V22" t="n">
-        <v>18.07616061288183</v>
-      </c>
-      <c r="W22" t="n">
-        <v>5.591087470473307</v>
-      </c>
-      <c r="X22" t="n">
-        <v>10.83626318319449</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2213,18 +1941,6 @@
       <c r="T23" t="n">
         <v>14</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.919345324483318</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.676682000621025</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.010828517773392</v>
-      </c>
-      <c r="X23" t="n">
-        <v>5.108130928576687</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2289,18 +2005,6 @@
       <c r="T24" t="n">
         <v>14</v>
       </c>
-      <c r="U24" t="n">
-        <v>7.455881464353956</v>
-      </c>
-      <c r="V24" t="n">
-        <v>11.50410439550554</v>
-      </c>
-      <c r="W24" t="n">
-        <v>7.810078449910204</v>
-      </c>
-      <c r="X24" t="n">
-        <v>11.23002664605027</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2365,18 +2069,6 @@
       <c r="T25" t="n">
         <v>14</v>
       </c>
-      <c r="U25" t="n">
-        <v>4.058061458949975</v>
-      </c>
-      <c r="V25" t="n">
-        <v>30.48947919361163</v>
-      </c>
-      <c r="W25" t="n">
-        <v>4.088124149213062</v>
-      </c>
-      <c r="X25" t="n">
-        <v>30.88290475849609</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2441,18 +2133,6 @@
       <c r="T26" t="n">
         <v>13</v>
       </c>
-      <c r="U26" t="n">
-        <v>0.5018724592078581</v>
-      </c>
-      <c r="V26" t="n">
-        <v>3.679939259250624</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.5001430595208627</v>
-      </c>
-      <c r="X26" t="n">
-        <v>25.88932083668216</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2517,18 +2197,6 @@
       <c r="T27" t="n">
         <v>13</v>
       </c>
-      <c r="U27" t="n">
-        <v>4.003792437489311</v>
-      </c>
-      <c r="V27" t="n">
-        <v>10.18264230265284</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.983080346770815</v>
-      </c>
-      <c r="X27" t="n">
-        <v>10.22941328922391</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2593,18 +2261,6 @@
       <c r="T28" t="n">
         <v>14</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.996145524761859</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.018822716258956</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.993176599926843</v>
-      </c>
-      <c r="X28" t="n">
-        <v>4.992081491111933</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2669,18 +2325,6 @@
       <c r="T29" t="n">
         <v>14</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.999959660097554</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.007084186875343</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.998966137836082</v>
-      </c>
-      <c r="X29" t="n">
-        <v>4.966522645488348</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2745,18 +2389,6 @@
       <c r="T30" t="n">
         <v>14</v>
       </c>
-      <c r="U30" t="n">
-        <v>5.987963014192163</v>
-      </c>
-      <c r="V30" t="n">
-        <v>25.47943384192479</v>
-      </c>
-      <c r="W30" t="n">
-        <v>4.019773524041816</v>
-      </c>
-      <c r="X30" t="n">
-        <v>15.55858518187717</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2821,18 +2453,6 @@
       <c r="T31" t="n">
         <v>14</v>
       </c>
-      <c r="U31" t="n">
-        <v>0.499824125519711</v>
-      </c>
-      <c r="V31" t="n">
-        <v>23.1933989242982</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.4998025627960983</v>
-      </c>
-      <c r="X31" t="n">
-        <v>22.53929511379573</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2897,18 +2517,6 @@
       <c r="T32" t="n">
         <v>14</v>
       </c>
-      <c r="U32" t="n">
-        <v>7.970053152787484</v>
-      </c>
-      <c r="V32" t="n">
-        <v>10.617861306074</v>
-      </c>
-      <c r="W32" t="n">
-        <v>7.967999738451826</v>
-      </c>
-      <c r="X32" t="n">
-        <v>10.65559265702142</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2973,18 +2581,6 @@
       <c r="T33" t="n">
         <v>14</v>
       </c>
-      <c r="U33" t="n">
-        <v>7.169981544411619</v>
-      </c>
-      <c r="V33" t="n">
-        <v>11.62095826835126</v>
-      </c>
-      <c r="W33" t="n">
-        <v>7.132017737094717</v>
-      </c>
-      <c r="X33" t="n">
-        <v>11.59193445717078</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3049,18 +2645,6 @@
       <c r="T34" t="n">
         <v>14</v>
       </c>
-      <c r="U34" t="n">
-        <v>5.929436380847489</v>
-      </c>
-      <c r="V34" t="n">
-        <v>11.77294147584461</v>
-      </c>
-      <c r="W34" t="n">
-        <v>5.727896660833954</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.31178920270637</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -3125,18 +2709,6 @@
       <c r="T35" t="n">
         <v>14</v>
       </c>
-      <c r="U35" t="n">
-        <v>4.547241900946599</v>
-      </c>
-      <c r="V35" t="n">
-        <v>12.44589431152802</v>
-      </c>
-      <c r="W35" t="n">
-        <v>4.086207807857649</v>
-      </c>
-      <c r="X35" t="n">
-        <v>9.780672598000272</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3201,18 +2773,6 @@
       <c r="T36" t="n">
         <v>14</v>
       </c>
-      <c r="U36" t="n">
-        <v>7.02911455416443</v>
-      </c>
-      <c r="V36" t="n">
-        <v>12.20182827971171</v>
-      </c>
-      <c r="W36" t="n">
-        <v>7.642394323205933</v>
-      </c>
-      <c r="X36" t="n">
-        <v>20.54673619202676</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3277,18 +2837,6 @@
       <c r="T37" t="n">
         <v>14</v>
       </c>
-      <c r="U37" t="n">
-        <v>1.852699348746591</v>
-      </c>
-      <c r="V37" t="n">
-        <v>4.306314549772257</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.83523284684627</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.889516274306716</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3353,18 +2901,6 @@
       <c r="T38" t="n">
         <v>14</v>
       </c>
-      <c r="U38" t="n">
-        <v>1.953001568435776</v>
-      </c>
-      <c r="V38" t="n">
-        <v>4.939242041277195</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.943019761615809</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.881174367604273</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3429,18 +2965,6 @@
       <c r="T39" t="n">
         <v>13</v>
       </c>
-      <c r="U39" t="n">
-        <v>2.753297046856039</v>
-      </c>
-      <c r="V39" t="n">
-        <v>5.071196455604555</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.642761842567452</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.850000384268837</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3505,18 +3029,6 @@
       <c r="T40" t="n">
         <v>13</v>
       </c>
-      <c r="U40" t="n">
-        <v>3.376018101080748</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.6404262083199</v>
-      </c>
-      <c r="W40" t="n">
-        <v>3.296857647609874</v>
-      </c>
-      <c r="X40" t="n">
-        <v>5.567837078189346</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3581,18 +3093,6 @@
       <c r="T41" t="n">
         <v>13</v>
       </c>
-      <c r="U41" t="n">
-        <v>4.129820668402254</v>
-      </c>
-      <c r="V41" t="n">
-        <v>9.445954092898738</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3.811236709631644</v>
-      </c>
-      <c r="X41" t="n">
-        <v>8.195873240408938</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3657,18 +3157,6 @@
       <c r="T42" t="n">
         <v>13</v>
       </c>
-      <c r="U42" t="n">
-        <v>3.027243463766293</v>
-      </c>
-      <c r="V42" t="n">
-        <v>5.581388840632534</v>
-      </c>
-      <c r="W42" t="n">
-        <v>4.462821295765051</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.836371782277372</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3733,18 +3221,6 @@
       <c r="T43" t="n">
         <v>13</v>
       </c>
-      <c r="U43" t="n">
-        <v>1.898208893187907</v>
-      </c>
-      <c r="V43" t="n">
-        <v>25.83556872336624</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.888665288824018</v>
-      </c>
-      <c r="X43" t="n">
-        <v>26.58030480834654</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3809,18 +3285,6 @@
       <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="U44" t="n">
-        <v>7.429815861850648</v>
-      </c>
-      <c r="V44" t="n">
-        <v>13.2308405098901</v>
-      </c>
-      <c r="W44" t="n">
-        <v>8.139608057405937</v>
-      </c>
-      <c r="X44" t="n">
-        <v>15.88544296164309</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3885,18 +3349,6 @@
       <c r="T45" t="n">
         <v>13</v>
       </c>
-      <c r="U45" t="n">
-        <v>3.993788868666381</v>
-      </c>
-      <c r="V45" t="n">
-        <v>28.63321899440345</v>
-      </c>
-      <c r="W45" t="n">
-        <v>4.013837817071549</v>
-      </c>
-      <c r="X45" t="n">
-        <v>28.46115055459657</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -3961,18 +3413,6 @@
       <c r="T46" t="n">
         <v>13</v>
       </c>
-      <c r="U46" t="n">
-        <v>1.932967155174628</v>
-      </c>
-      <c r="V46" t="n">
-        <v>4.760984210088502</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.909175405900655</v>
-      </c>
-      <c r="X46" t="n">
-        <v>4.586961677378254</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -4037,18 +3477,6 @@
       <c r="T47" t="n">
         <v>12</v>
       </c>
-      <c r="U47" t="n">
-        <v>5.920891391728165</v>
-      </c>
-      <c r="V47" t="n">
-        <v>39.92329908888599</v>
-      </c>
-      <c r="W47" t="n">
-        <v>4.129283718036284</v>
-      </c>
-      <c r="X47" t="n">
-        <v>25.01856803757103</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4113,18 +3541,6 @@
       <c r="T48" t="n">
         <v>12</v>
       </c>
-      <c r="U48" t="n">
-        <v>0.5006737409011446</v>
-      </c>
-      <c r="V48" t="n">
-        <v>19.6133642795486</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0.5011560347098287</v>
-      </c>
-      <c r="X48" t="n">
-        <v>18.40838666890335</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -4189,18 +3605,6 @@
       <c r="T49" t="n">
         <v>12</v>
       </c>
-      <c r="U49" t="n">
-        <v>8.159146651585772</v>
-      </c>
-      <c r="V49" t="n">
-        <v>10.58950646527972</v>
-      </c>
-      <c r="W49" t="n">
-        <v>6.069641613639682</v>
-      </c>
-      <c r="X49" t="n">
-        <v>10.22745766766127</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -4265,18 +3669,6 @@
       <c r="T50" t="n">
         <v>12</v>
       </c>
-      <c r="U50" t="n">
-        <v>0.5014443400132379</v>
-      </c>
-      <c r="V50" t="n">
-        <v>15.57011027521158</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0.5022245298818497</v>
-      </c>
-      <c r="X50" t="n">
-        <v>13.15258888850056</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4341,18 +3733,6 @@
       <c r="T51" t="n">
         <v>13</v>
       </c>
-      <c r="U51" t="n">
-        <v>0.5015113423488657</v>
-      </c>
-      <c r="V51" t="n">
-        <v>13.30051078284729</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.815344039247886</v>
-      </c>
-      <c r="X51" t="n">
-        <v>18.57883640127298</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -4417,18 +3797,6 @@
       <c r="T52" t="n">
         <v>14</v>
       </c>
-      <c r="U52" t="n">
-        <v>0.5012144960693993</v>
-      </c>
-      <c r="V52" t="n">
-        <v>13.9990842926314</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.875130595750449</v>
-      </c>
-      <c r="X52" t="n">
-        <v>24.54094952523847</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4493,18 +3861,6 @@
       <c r="T53" t="n">
         <v>14</v>
       </c>
-      <c r="U53" t="n">
-        <v>4.262060265272858</v>
-      </c>
-      <c r="V53" t="n">
-        <v>30.0132096965191</v>
-      </c>
-      <c r="W53" t="n">
-        <v>4.384155107902123</v>
-      </c>
-      <c r="X53" t="n">
-        <v>31.24523551534333</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4569,18 +3925,6 @@
       <c r="T54" t="n">
         <v>14</v>
       </c>
-      <c r="U54" t="n">
-        <v>0.5018136339474846</v>
-      </c>
-      <c r="V54" t="n">
-        <v>11.62918134438163</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0.5023978624913316</v>
-      </c>
-      <c r="X54" t="n">
-        <v>13.16451427124168</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -4645,18 +3989,6 @@
       <c r="T55" t="n">
         <v>14</v>
       </c>
-      <c r="U55" t="n">
-        <v>0.5020930761742263</v>
-      </c>
-      <c r="V55" t="n">
-        <v>13.15752144153962</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0.5022657546624967</v>
-      </c>
-      <c r="X55" t="n">
-        <v>13.02446757931121</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -4721,18 +4053,6 @@
       <c r="T56" t="n">
         <v>12</v>
       </c>
-      <c r="U56" t="n">
-        <v>0.5020605735401983</v>
-      </c>
-      <c r="V56" t="n">
-        <v>12.80340905797722</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.952840420389451</v>
-      </c>
-      <c r="X56" t="n">
-        <v>4.664732359625511</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -4797,18 +4117,6 @@
       <c r="T57" t="n">
         <v>14</v>
       </c>
-      <c r="U57" t="n">
-        <v>0.5010049882385432</v>
-      </c>
-      <c r="V57" t="n">
-        <v>14.43744083922383</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.987881597039232</v>
-      </c>
-      <c r="X57" t="n">
-        <v>14.97439191756457</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -4873,18 +4181,6 @@
       <c r="T58" t="n">
         <v>15</v>
       </c>
-      <c r="U58" t="n">
-        <v>1.991659118780896</v>
-      </c>
-      <c r="V58" t="n">
-        <v>9.98782901000355</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.988922141089994</v>
-      </c>
-      <c r="X58" t="n">
-        <v>9.997118708327724</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -4949,18 +4245,6 @@
       <c r="T59" t="n">
         <v>15</v>
       </c>
-      <c r="U59" t="n">
-        <v>0.5003919688203879</v>
-      </c>
-      <c r="V59" t="n">
-        <v>13.92328366718042</v>
-      </c>
-      <c r="W59" t="n">
-        <v>3.98273044351268</v>
-      </c>
-      <c r="X59" t="n">
-        <v>30.00706025397247</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -5025,18 +4309,6 @@
       <c r="T60" t="n">
         <v>14</v>
       </c>
-      <c r="U60" t="n">
-        <v>5.952213431529116</v>
-      </c>
-      <c r="V60" t="n">
-        <v>32.41954625763221</v>
-      </c>
-      <c r="W60" t="n">
-        <v>5.937398066315532</v>
-      </c>
-      <c r="X60" t="n">
-        <v>32.55003563630299</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -5101,18 +4373,6 @@
       <c r="T61" t="n">
         <v>14</v>
       </c>
-      <c r="U61" t="n">
-        <v>6.525717624968607</v>
-      </c>
-      <c r="V61" t="n">
-        <v>28.79544392344872</v>
-      </c>
-      <c r="W61" t="n">
-        <v>6.58271000585962</v>
-      </c>
-      <c r="X61" t="n">
-        <v>29.84164090932215</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -5177,18 +4437,6 @@
       <c r="T62" t="n">
         <v>13</v>
       </c>
-      <c r="U62" t="n">
-        <v>2.002981437848184</v>
-      </c>
-      <c r="V62" t="n">
-        <v>5.059790024518468</v>
-      </c>
-      <c r="W62" t="n">
-        <v>2.004971308108309</v>
-      </c>
-      <c r="X62" t="n">
-        <v>5.073675118994532</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -5253,18 +4501,6 @@
       <c r="T63" t="n">
         <v>13</v>
       </c>
-      <c r="U63" t="n">
-        <v>1.924723653654916</v>
-      </c>
-      <c r="V63" t="n">
-        <v>4.581188226380716</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.918698217555796</v>
-      </c>
-      <c r="X63" t="n">
-        <v>4.547398078164146</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -5329,18 +4565,6 @@
       <c r="T64" t="n">
         <v>13</v>
       </c>
-      <c r="U64" t="n">
-        <v>8.102239596490969</v>
-      </c>
-      <c r="V64" t="n">
-        <v>37.33312597004181</v>
-      </c>
-      <c r="W64" t="n">
-        <v>3.117092139329604</v>
-      </c>
-      <c r="X64" t="n">
-        <v>5.069154407269237</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -5405,18 +4629,6 @@
       <c r="T65" t="n">
         <v>14</v>
       </c>
-      <c r="U65" t="n">
-        <v>1.86637378087802</v>
-      </c>
-      <c r="V65" t="n">
-        <v>4.317855122165124</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.848603715415186</v>
-      </c>
-      <c r="X65" t="n">
-        <v>4.230219675116357</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -5481,18 +4693,6 @@
       <c r="T66" t="n">
         <v>14</v>
       </c>
-      <c r="U66" t="n">
-        <v>0.5009436117498955</v>
-      </c>
-      <c r="V66" t="n">
-        <v>10.19798465632603</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.875672375541094</v>
-      </c>
-      <c r="X66" t="n">
-        <v>4.438485306814242</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -5557,18 +4757,6 @@
       <c r="T67" t="n">
         <v>14</v>
       </c>
-      <c r="U67" t="n">
-        <v>3.142312105402743</v>
-      </c>
-      <c r="V67" t="n">
-        <v>5.220171984488083</v>
-      </c>
-      <c r="W67" t="n">
-        <v>3.072206292193296</v>
-      </c>
-      <c r="X67" t="n">
-        <v>5.127049630261581</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -5633,18 +4821,6 @@
       <c r="T68" t="n">
         <v>14</v>
       </c>
-      <c r="U68" t="n">
-        <v>1.984738696753238</v>
-      </c>
-      <c r="V68" t="n">
-        <v>4.9210354626499</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.985935101666512</v>
-      </c>
-      <c r="X68" t="n">
-        <v>4.928557922737748</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -5709,18 +4885,6 @@
       <c r="T69" t="n">
         <v>14</v>
       </c>
-      <c r="U69" t="n">
-        <v>0.5001132008320308</v>
-      </c>
-      <c r="V69" t="n">
-        <v>11.37039403194649</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0.5000024655478578</v>
-      </c>
-      <c r="X69" t="n">
-        <v>11.39915241323181</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -5785,18 +4949,6 @@
       <c r="T70" t="n">
         <v>15</v>
       </c>
-      <c r="U70" t="n">
-        <v>1.999891042491977</v>
-      </c>
-      <c r="V70" t="n">
-        <v>5.000941212480383</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1.999257080057656</v>
-      </c>
-      <c r="X70" t="n">
-        <v>4.999628022331088</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -5861,18 +5013,6 @@
       <c r="T71" t="n">
         <v>15</v>
       </c>
-      <c r="U71" t="n">
-        <v>0.4998218240278524</v>
-      </c>
-      <c r="V71" t="n">
-        <v>12.69715373954226</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0.4997922051951214</v>
-      </c>
-      <c r="X71" t="n">
-        <v>12.60916179734118</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -5937,18 +5077,6 @@
       <c r="T72" t="n">
         <v>15</v>
       </c>
-      <c r="U72" t="n">
-        <v>0.4999088310127572</v>
-      </c>
-      <c r="V72" t="n">
-        <v>11.52413137137806</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0.4998058566655349</v>
-      </c>
-      <c r="X72" t="n">
-        <v>11.67676637922368</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -6013,18 +5141,6 @@
       <c r="T73" t="n">
         <v>15</v>
       </c>
-      <c r="U73" t="n">
-        <v>0.4998643862353229</v>
-      </c>
-      <c r="V73" t="n">
-        <v>9.332319132457798</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0.4998668157685637</v>
-      </c>
-      <c r="X73" t="n">
-        <v>22.9991951073655</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -6089,18 +5205,6 @@
       <c r="T74" t="n">
         <v>14</v>
       </c>
-      <c r="U74" t="n">
-        <v>0.4997399264726107</v>
-      </c>
-      <c r="V74" t="n">
-        <v>9.690742353547201</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0.4999369275146101</v>
-      </c>
-      <c r="X74" t="n">
-        <v>9.648476162570233</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -6165,18 +5269,6 @@
       <c r="T75" t="n">
         <v>14</v>
       </c>
-      <c r="U75" t="n">
-        <v>0.5000857842368397</v>
-      </c>
-      <c r="V75" t="n">
-        <v>29.68703585415743</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0.4999006991329994</v>
-      </c>
-      <c r="X75" t="n">
-        <v>29.97448184072089</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -6241,18 +5333,6 @@
       <c r="T76" t="n">
         <v>14</v>
       </c>
-      <c r="U76" t="n">
-        <v>2.00998878699292</v>
-      </c>
-      <c r="V76" t="n">
-        <v>14.14345715100985</v>
-      </c>
-      <c r="W76" t="n">
-        <v>2.016517967593134</v>
-      </c>
-      <c r="X76" t="n">
-        <v>14.54234138634827</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -6317,18 +5397,6 @@
       <c r="T77" t="n">
         <v>14</v>
       </c>
-      <c r="U77" t="n">
-        <v>2.0125710664799</v>
-      </c>
-      <c r="V77" t="n">
-        <v>16.64556966527131</v>
-      </c>
-      <c r="W77" t="n">
-        <v>2.02612229699771</v>
-      </c>
-      <c r="X77" t="n">
-        <v>13.1257674974365</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -6393,18 +5461,6 @@
       <c r="T78" t="n">
         <v>14</v>
       </c>
-      <c r="U78" t="n">
-        <v>0.500209829044366</v>
-      </c>
-      <c r="V78" t="n">
-        <v>10.88494906963995</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0.5003938054126132</v>
-      </c>
-      <c r="X78" t="n">
-        <v>10.81371362466715</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -6469,18 +5525,6 @@
       <c r="T79" t="n">
         <v>14</v>
       </c>
-      <c r="U79" t="n">
-        <v>2.015012618731591</v>
-      </c>
-      <c r="V79" t="n">
-        <v>10.48073058411487</v>
-      </c>
-      <c r="W79" t="n">
-        <v>2.015858686907191</v>
-      </c>
-      <c r="X79" t="n">
-        <v>10.40482384591276</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -6545,18 +5589,6 @@
       <c r="T80" t="n">
         <v>13</v>
       </c>
-      <c r="U80" t="n">
-        <v>1.985509860083659</v>
-      </c>
-      <c r="V80" t="n">
-        <v>5.013973431809441</v>
-      </c>
-      <c r="W80" t="n">
-        <v>1.983307817630213</v>
-      </c>
-      <c r="X80" t="n">
-        <v>5.002980372176793</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -6621,18 +5653,6 @@
       <c r="T81" t="n">
         <v>13</v>
       </c>
-      <c r="U81" t="n">
-        <v>2.003380694955093</v>
-      </c>
-      <c r="V81" t="n">
-        <v>5.098800708611702</v>
-      </c>
-      <c r="W81" t="n">
-        <v>1.998708031613956</v>
-      </c>
-      <c r="X81" t="n">
-        <v>5.084817282697665</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -6697,18 +5717,6 @@
       <c r="T82" t="n">
         <v>14</v>
       </c>
-      <c r="U82" t="n">
-        <v>0.4995946493427465</v>
-      </c>
-      <c r="V82" t="n">
-        <v>5.613874236437986</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0.4997227056856479</v>
-      </c>
-      <c r="X82" t="n">
-        <v>24.16104007478498</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -6773,18 +5781,6 @@
       <c r="T83" t="n">
         <v>14</v>
       </c>
-      <c r="U83" t="n">
-        <v>0.4994361086768066</v>
-      </c>
-      <c r="V83" t="n">
-        <v>5.86809123399053</v>
-      </c>
-      <c r="W83" t="n">
-        <v>1.978344453406815</v>
-      </c>
-      <c r="X83" t="n">
-        <v>4.962405548402977</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -6849,18 +5845,6 @@
       <c r="T84" t="n">
         <v>14</v>
       </c>
-      <c r="U84" t="n">
-        <v>2.01444276536835</v>
-      </c>
-      <c r="V84" t="n">
-        <v>4.976590554308772</v>
-      </c>
-      <c r="W84" t="n">
-        <v>2.01728006955909</v>
-      </c>
-      <c r="X84" t="n">
-        <v>5.006310418167593</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -6925,18 +5909,6 @@
       <c r="T85" t="n">
         <v>14</v>
       </c>
-      <c r="U85" t="n">
-        <v>1.997354885842489</v>
-      </c>
-      <c r="V85" t="n">
-        <v>5.086876447194662</v>
-      </c>
-      <c r="W85" t="n">
-        <v>1.994295150910254</v>
-      </c>
-      <c r="X85" t="n">
-        <v>5.077235022802067</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -7001,18 +5973,6 @@
       <c r="T86" t="n">
         <v>14</v>
       </c>
-      <c r="U86" t="n">
-        <v>1.936494537442589</v>
-      </c>
-      <c r="V86" t="n">
-        <v>4.771585710602478</v>
-      </c>
-      <c r="W86" t="n">
-        <v>1.924313772815046</v>
-      </c>
-      <c r="X86" t="n">
-        <v>4.676168905743978</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -7077,18 +6037,6 @@
       <c r="T87" t="n">
         <v>14</v>
       </c>
-      <c r="U87" t="n">
-        <v>2.007813108763992</v>
-      </c>
-      <c r="V87" t="n">
-        <v>4.992222292614372</v>
-      </c>
-      <c r="W87" t="n">
-        <v>2.010188443939947</v>
-      </c>
-      <c r="X87" t="n">
-        <v>10.86128008338041</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -7153,18 +6101,6 @@
       <c r="T88" t="n">
         <v>14</v>
       </c>
-      <c r="U88" t="n">
-        <v>2.01186238429435</v>
-      </c>
-      <c r="V88" t="n">
-        <v>5.007028344001837</v>
-      </c>
-      <c r="W88" t="n">
-        <v>2.013047773898693</v>
-      </c>
-      <c r="X88" t="n">
-        <v>5.014676289776699</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -7229,18 +6165,6 @@
       <c r="T89" t="n">
         <v>14</v>
       </c>
-      <c r="U89" t="n">
-        <v>2.015007977855853</v>
-      </c>
-      <c r="V89" t="n">
-        <v>5.050707720945371</v>
-      </c>
-      <c r="W89" t="n">
-        <v>2.016712366980768</v>
-      </c>
-      <c r="X89" t="n">
-        <v>5.060836692331213</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -7305,18 +6229,6 @@
       <c r="T90" t="n">
         <v>13</v>
       </c>
-      <c r="U90" t="n">
-        <v>2.014676846472332</v>
-      </c>
-      <c r="V90" t="n">
-        <v>13.41845538483552</v>
-      </c>
-      <c r="W90" t="n">
-        <v>2.021446458418214</v>
-      </c>
-      <c r="X90" t="n">
-        <v>13.72294025455585</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -7381,18 +6293,6 @@
       <c r="T91" t="n">
         <v>13</v>
       </c>
-      <c r="U91" t="n">
-        <v>2.023394387319962</v>
-      </c>
-      <c r="V91" t="n">
-        <v>5.029406381451915</v>
-      </c>
-      <c r="W91" t="n">
-        <v>2.028745090559672</v>
-      </c>
-      <c r="X91" t="n">
-        <v>5.041548072734169</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -7457,18 +6357,6 @@
       <c r="T92" t="n">
         <v>13</v>
       </c>
-      <c r="U92" t="n">
-        <v>0.4990915466080194</v>
-      </c>
-      <c r="V92" t="n">
-        <v>7.251176949161112</v>
-      </c>
-      <c r="W92" t="n">
-        <v>1.968942810564845</v>
-      </c>
-      <c r="X92" t="n">
-        <v>4.992954669096388</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -7533,18 +6421,6 @@
       <c r="T93" t="n">
         <v>13</v>
       </c>
-      <c r="U93" t="n">
-        <v>4.009212253099365</v>
-      </c>
-      <c r="V93" t="n">
-        <v>10.50063359791714</v>
-      </c>
-      <c r="W93" t="n">
-        <v>3.996717704363485</v>
-      </c>
-      <c r="X93" t="n">
-        <v>10.46906506378123</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -7609,18 +6485,6 @@
       <c r="T94" t="n">
         <v>13</v>
       </c>
-      <c r="U94" t="n">
-        <v>2.002032286915052</v>
-      </c>
-      <c r="V94" t="n">
-        <v>5.00701748652939</v>
-      </c>
-      <c r="W94" t="n">
-        <v>2.002830527239075</v>
-      </c>
-      <c r="X94" t="n">
-        <v>4.998648578131953</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -7685,18 +6549,6 @@
       <c r="T95" t="n">
         <v>13</v>
       </c>
-      <c r="U95" t="n">
-        <v>4.002961758834727</v>
-      </c>
-      <c r="V95" t="n">
-        <v>10.19919588327784</v>
-      </c>
-      <c r="W95" t="n">
-        <v>4.006413284537188</v>
-      </c>
-      <c r="X95" t="n">
-        <v>10.25844989536682</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -7761,18 +6613,6 @@
       <c r="T96" t="n">
         <v>14</v>
       </c>
-      <c r="U96" t="n">
-        <v>5.378749481386685</v>
-      </c>
-      <c r="V96" t="n">
-        <v>49.99999999914621</v>
-      </c>
-      <c r="W96" t="n">
-        <v>4.56068869669273</v>
-      </c>
-      <c r="X96" t="n">
-        <v>14.32336186345685</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -7837,18 +6677,6 @@
       <c r="T97" t="n">
         <v>14</v>
       </c>
-      <c r="U97" t="n">
-        <v>6.188334117332978</v>
-      </c>
-      <c r="V97" t="n">
-        <v>22.6774101009611</v>
-      </c>
-      <c r="W97" t="n">
-        <v>6.046493540307955</v>
-      </c>
-      <c r="X97" t="n">
-        <v>21.79159347009275</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -7913,18 +6741,6 @@
       <c r="T98" t="n">
         <v>14</v>
       </c>
-      <c r="U98" t="n">
-        <v>1.939074207572671</v>
-      </c>
-      <c r="V98" t="n">
-        <v>4.881786578110058</v>
-      </c>
-      <c r="W98" t="n">
-        <v>4.292143345742826</v>
-      </c>
-      <c r="X98" t="n">
-        <v>2.72090383053131</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -7989,18 +6805,6 @@
       <c r="T99" t="n">
         <v>13</v>
       </c>
-      <c r="U99" t="n">
-        <v>3.481470371760784</v>
-      </c>
-      <c r="V99" t="n">
-        <v>7.650381191008247</v>
-      </c>
-      <c r="W99" t="n">
-        <v>3.36466890981876</v>
-      </c>
-      <c r="X99" t="n">
-        <v>9.110104826041539</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -8065,18 +6869,6 @@
       <c r="T100" t="n">
         <v>13</v>
       </c>
-      <c r="U100" t="n">
-        <v>4.875208151234758</v>
-      </c>
-      <c r="V100" t="n">
-        <v>10.86780650093356</v>
-      </c>
-      <c r="W100" t="n">
-        <v>8.833917749230904</v>
-      </c>
-      <c r="X100" t="n">
-        <v>4.712746924097715</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -8141,18 +6933,6 @@
       <c r="T101" t="n">
         <v>13</v>
       </c>
-      <c r="U101" t="n">
-        <v>4.61156103574924</v>
-      </c>
-      <c r="V101" t="n">
-        <v>39.55147065226804</v>
-      </c>
-      <c r="W101" t="n">
-        <v>4.607876093897072</v>
-      </c>
-      <c r="X101" t="n">
-        <v>15.34186322531525</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -8217,18 +6997,6 @@
       <c r="T102" t="n">
         <v>13</v>
       </c>
-      <c r="U102" t="n">
-        <v>2.001446088219053</v>
-      </c>
-      <c r="V102" t="n">
-        <v>5.02906504487544</v>
-      </c>
-      <c r="W102" t="n">
-        <v>2.002293317478252</v>
-      </c>
-      <c r="X102" t="n">
-        <v>5.040427322790003</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -8293,18 +7061,6 @@
       <c r="T103" t="n">
         <v>13</v>
       </c>
-      <c r="U103" t="n">
-        <v>2.012639529654427</v>
-      </c>
-      <c r="V103" t="n">
-        <v>5.138932636949583</v>
-      </c>
-      <c r="W103" t="n">
-        <v>2.0132702972366</v>
-      </c>
-      <c r="X103" t="n">
-        <v>5.151924287358153</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -8369,18 +7125,6 @@
       <c r="T104" t="n">
         <v>13</v>
       </c>
-      <c r="U104" t="n">
-        <v>7.059129139750383</v>
-      </c>
-      <c r="V104" t="n">
-        <v>9.966694685634204</v>
-      </c>
-      <c r="W104" t="n">
-        <v>6.908938293148097</v>
-      </c>
-      <c r="X104" t="n">
-        <v>10.05430370211234</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -8445,18 +7189,6 @@
       <c r="T105" t="n">
         <v>13</v>
       </c>
-      <c r="U105" t="n">
-        <v>6.547697069594812</v>
-      </c>
-      <c r="V105" t="n">
-        <v>10.54003620330596</v>
-      </c>
-      <c r="W105" t="n">
-        <v>6.450949390672928</v>
-      </c>
-      <c r="X105" t="n">
-        <v>10.68327740801537</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -8521,18 +7253,6 @@
       <c r="T106" t="n">
         <v>13</v>
       </c>
-      <c r="U106" t="n">
-        <v>1.779176959948867</v>
-      </c>
-      <c r="V106" t="n">
-        <v>3.961559461018199</v>
-      </c>
-      <c r="W106" t="n">
-        <v>2.307216514468336</v>
-      </c>
-      <c r="X106" t="n">
-        <v>4.061639618133269</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -8597,18 +7317,6 @@
       <c r="T107" t="n">
         <v>12</v>
       </c>
-      <c r="U107" t="n">
-        <v>2.067689311510821</v>
-      </c>
-      <c r="V107" t="n">
-        <v>3.944140517550189</v>
-      </c>
-      <c r="W107" t="n">
-        <v>2.225508581071144</v>
-      </c>
-      <c r="X107" t="n">
-        <v>4.513178146084051</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -8673,18 +7381,6 @@
       <c r="T108" t="n">
         <v>12</v>
       </c>
-      <c r="U108" t="n">
-        <v>0.501358089440499</v>
-      </c>
-      <c r="V108" t="n">
-        <v>9.092386644387283</v>
-      </c>
-      <c r="W108" t="n">
-        <v>1.651692623864585</v>
-      </c>
-      <c r="X108" t="n">
-        <v>3.753561476241248</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -8749,18 +7445,6 @@
       <c r="T109" t="n">
         <v>12</v>
       </c>
-      <c r="U109" t="n">
-        <v>0.5001805175738797</v>
-      </c>
-      <c r="V109" t="n">
-        <v>13.5571087101335</v>
-      </c>
-      <c r="W109" t="n">
-        <v>0.5000833359212036</v>
-      </c>
-      <c r="X109" t="n">
-        <v>13.39690026957271</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -8825,18 +7509,6 @@
       <c r="T110" t="n">
         <v>11</v>
       </c>
-      <c r="U110" t="n">
-        <v>0.5028056426601399</v>
-      </c>
-      <c r="V110" t="n">
-        <v>10.12235420959594</v>
-      </c>
-      <c r="W110" t="n">
-        <v>0.5031175823757831</v>
-      </c>
-      <c r="X110" t="n">
-        <v>9.842052505742245</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -8901,18 +7573,6 @@
       <c r="T111" t="n">
         <v>11</v>
       </c>
-      <c r="U111" t="n">
-        <v>0.502407890244586</v>
-      </c>
-      <c r="V111" t="n">
-        <v>11.83747259945546</v>
-      </c>
-      <c r="W111" t="n">
-        <v>0.5031110922183937</v>
-      </c>
-      <c r="X111" t="n">
-        <v>13.69549408897369</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -8977,18 +7637,6 @@
       <c r="T112" t="n">
         <v>11</v>
       </c>
-      <c r="U112" t="n">
-        <v>0.5039970814422317</v>
-      </c>
-      <c r="V112" t="n">
-        <v>2.937808766808055</v>
-      </c>
-      <c r="W112" t="n">
-        <v>0.4999199370083541</v>
-      </c>
-      <c r="X112" t="n">
-        <v>20.32045617683011</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -9053,18 +7701,6 @@
       <c r="T113" t="n">
         <v>11</v>
       </c>
-      <c r="U113" t="n">
-        <v>0.5034772693601504</v>
-      </c>
-      <c r="V113" t="n">
-        <v>14.3836916947518</v>
-      </c>
-      <c r="W113" t="n">
-        <v>0.5043272165412113</v>
-      </c>
-      <c r="X113" t="n">
-        <v>14.79528023873096</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -9129,18 +7765,6 @@
       <c r="T114" t="n">
         <v>11</v>
       </c>
-      <c r="U114" t="n">
-        <v>0.5057470576911408</v>
-      </c>
-      <c r="V114" t="n">
-        <v>10.96828913185532</v>
-      </c>
-      <c r="W114" t="n">
-        <v>1.707771936955952</v>
-      </c>
-      <c r="X114" t="n">
-        <v>3.823392563657352</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -9205,18 +7829,6 @@
       <c r="T115" t="n">
         <v>11</v>
       </c>
-      <c r="U115" t="n">
-        <v>0.5044023596675196</v>
-      </c>
-      <c r="V115" t="n">
-        <v>12.3679290492917</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0.504052380370002</v>
-      </c>
-      <c r="X115" t="n">
-        <v>10.24276303627018</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -9281,18 +7893,6 @@
       <c r="T116" t="n">
         <v>11</v>
       </c>
-      <c r="U116" t="n">
-        <v>0.5048121371731868</v>
-      </c>
-      <c r="V116" t="n">
-        <v>8.733591566322776</v>
-      </c>
-      <c r="W116" t="n">
-        <v>0.5051291880681221</v>
-      </c>
-      <c r="X116" t="n">
-        <v>8.466002809180035</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -9357,18 +7957,6 @@
       <c r="T117" t="n">
         <v>11</v>
       </c>
-      <c r="U117" t="n">
-        <v>0.5047450305000947</v>
-      </c>
-      <c r="V117" t="n">
-        <v>7.023576924378681</v>
-      </c>
-      <c r="W117" t="n">
-        <v>0.5053982634932584</v>
-      </c>
-      <c r="X117" t="n">
-        <v>6.871631224676999</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -9433,18 +8021,6 @@
       <c r="T118" t="n">
         <v>10</v>
       </c>
-      <c r="U118" t="n">
-        <v>0.5050560534775592</v>
-      </c>
-      <c r="V118" t="n">
-        <v>6.810099416275074</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0.5054911665226046</v>
-      </c>
-      <c r="X118" t="n">
-        <v>6.738040692992426</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -9509,18 +8085,6 @@
       <c r="T119" t="n">
         <v>10</v>
       </c>
-      <c r="U119" t="n">
-        <v>0.506119901841329</v>
-      </c>
-      <c r="V119" t="n">
-        <v>7.023034502286994</v>
-      </c>
-      <c r="W119" t="n">
-        <v>0.5069554248977824</v>
-      </c>
-      <c r="X119" t="n">
-        <v>6.903177749468735</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -9585,18 +8149,6 @@
       <c r="T120" t="n">
         <v>10</v>
       </c>
-      <c r="U120" t="n">
-        <v>0.5054719682131544</v>
-      </c>
-      <c r="V120" t="n">
-        <v>7.666668102658668</v>
-      </c>
-      <c r="W120" t="n">
-        <v>0.5061383851155001</v>
-      </c>
-      <c r="X120" t="n">
-        <v>7.58289700093655</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -9661,18 +8213,6 @@
       <c r="T121" t="n">
         <v>10</v>
       </c>
-      <c r="U121" t="n">
-        <v>0.5060728033967704</v>
-      </c>
-      <c r="V121" t="n">
-        <v>8.015930776898569</v>
-      </c>
-      <c r="W121" t="n">
-        <v>0.5070013255826922</v>
-      </c>
-      <c r="X121" t="n">
-        <v>7.859658359891838</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -9737,18 +8277,6 @@
       <c r="T122" t="n">
         <v>10</v>
       </c>
-      <c r="U122" t="n">
-        <v>0.5060540297433759</v>
-      </c>
-      <c r="V122" t="n">
-        <v>8.621080559486925</v>
-      </c>
-      <c r="W122" t="n">
-        <v>0.5069681460434389</v>
-      </c>
-      <c r="X122" t="n">
-        <v>8.422374220282629</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -9813,18 +8341,6 @@
       <c r="T123" t="n">
         <v>10</v>
       </c>
-      <c r="U123" t="n">
-        <v>0.5033365346290561</v>
-      </c>
-      <c r="V123" t="n">
-        <v>9.139895529857114</v>
-      </c>
-      <c r="W123" t="n">
-        <v>0.5038228629422523</v>
-      </c>
-      <c r="X123" t="n">
-        <v>9.069640853859431</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -9889,18 +8405,6 @@
       <c r="T124" t="n">
         <v>10</v>
       </c>
-      <c r="U124" t="n">
-        <v>0.5025663346559104</v>
-      </c>
-      <c r="V124" t="n">
-        <v>12.51673251538584</v>
-      </c>
-      <c r="W124" t="n">
-        <v>0.5028522234232343</v>
-      </c>
-      <c r="X124" t="n">
-        <v>9.726156652861667</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -9965,18 +8469,6 @@
       <c r="T125" t="n">
         <v>10</v>
       </c>
-      <c r="U125" t="n">
-        <v>0.5020324601641885</v>
-      </c>
-      <c r="V125" t="n">
-        <v>10.26524192538582</v>
-      </c>
-      <c r="W125" t="n">
-        <v>0.5022896260481552</v>
-      </c>
-      <c r="X125" t="n">
-        <v>10.16126024145317</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -10041,18 +8533,6 @@
       <c r="T126" t="n">
         <v>10</v>
       </c>
-      <c r="U126" t="n">
-        <v>0.5011987404032803</v>
-      </c>
-      <c r="V126" t="n">
-        <v>12.39898525015581</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0.500977476311939</v>
-      </c>
-      <c r="X126" t="n">
-        <v>9.769979554391865</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -10117,18 +8597,6 @@
       <c r="T127" t="n">
         <v>10</v>
       </c>
-      <c r="U127" t="n">
-        <v>0.5006559478801343</v>
-      </c>
-      <c r="V127" t="n">
-        <v>12.66475910510205</v>
-      </c>
-      <c r="W127" t="n">
-        <v>0.5006029298539889</v>
-      </c>
-      <c r="X127" t="n">
-        <v>12.62097323789341</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -10193,18 +8661,6 @@
       <c r="T128" t="n">
         <v>10</v>
       </c>
-      <c r="U128" t="n">
-        <v>1.999838028394566</v>
-      </c>
-      <c r="V128" t="n">
-        <v>9.936530968283586</v>
-      </c>
-      <c r="W128" t="n">
-        <v>2.000436147514644</v>
-      </c>
-      <c r="X128" t="n">
-        <v>10.0454368541851</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -10269,18 +8725,6 @@
       <c r="T129" t="n">
         <v>10</v>
       </c>
-      <c r="U129" t="n">
-        <v>0.5003078586122284</v>
-      </c>
-      <c r="V129" t="n">
-        <v>15.61076116885248</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0.5000200657889607</v>
-      </c>
-      <c r="X129" t="n">
-        <v>18.52977855920851</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -10345,18 +8789,6 @@
       <c r="T130" t="n">
         <v>10</v>
       </c>
-      <c r="U130" t="n">
-        <v>1.997714952712023</v>
-      </c>
-      <c r="V130" t="n">
-        <v>4.975155883958133</v>
-      </c>
-      <c r="W130" t="n">
-        <v>1.996423688790695</v>
-      </c>
-      <c r="X130" t="n">
-        <v>4.954128047845008</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -10421,18 +8853,6 @@
       <c r="T131" t="n">
         <v>10</v>
       </c>
-      <c r="U131" t="n">
-        <v>1.904885658266567</v>
-      </c>
-      <c r="V131" t="n">
-        <v>4.448068536736145</v>
-      </c>
-      <c r="W131" t="n">
-        <v>1.890912761345844</v>
-      </c>
-      <c r="X131" t="n">
-        <v>4.344503287660608</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -10497,18 +8917,6 @@
       <c r="T132" t="n">
         <v>10</v>
       </c>
-      <c r="U132" t="n">
-        <v>1.95565822392347</v>
-      </c>
-      <c r="V132" t="n">
-        <v>4.756799931333298</v>
-      </c>
-      <c r="W132" t="n">
-        <v>1.944404313918656</v>
-      </c>
-      <c r="X132" t="n">
-        <v>4.67255422373518</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -10573,18 +8981,6 @@
       <c r="T133" t="n">
         <v>9</v>
       </c>
-      <c r="U133" t="n">
-        <v>1.964009036014863</v>
-      </c>
-      <c r="V133" t="n">
-        <v>4.813380339833022</v>
-      </c>
-      <c r="W133" t="n">
-        <v>1.963884769991649</v>
-      </c>
-      <c r="X133" t="n">
-        <v>4.796657521678131</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -10649,18 +9045,6 @@
       <c r="T134" t="n">
         <v>9</v>
       </c>
-      <c r="U134" t="n">
-        <v>0.5027874065065149</v>
-      </c>
-      <c r="V134" t="n">
-        <v>6.188123107652354</v>
-      </c>
-      <c r="W134" t="n">
-        <v>1.925791969164037</v>
-      </c>
-      <c r="X134" t="n">
-        <v>4.078188555615817</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -10725,18 +9109,6 @@
       <c r="T135" t="n">
         <v>10</v>
       </c>
-      <c r="U135" t="n">
-        <v>0.5015540648641049</v>
-      </c>
-      <c r="V135" t="n">
-        <v>9.897788660515541</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0.5017763890866551</v>
-      </c>
-      <c r="X135" t="n">
-        <v>6.037755451712622</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -10801,18 +9173,6 @@
       <c r="T136" t="n">
         <v>10</v>
       </c>
-      <c r="U136" t="n">
-        <v>3.991218525307189</v>
-      </c>
-      <c r="V136" t="n">
-        <v>16.03530168036347</v>
-      </c>
-      <c r="W136" t="n">
-        <v>3.983951313889546</v>
-      </c>
-      <c r="X136" t="n">
-        <v>16.11742558296439</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -10877,18 +9237,6 @@
       <c r="T137" t="n">
         <v>10</v>
       </c>
-      <c r="U137" t="n">
-        <v>4.017753015952631</v>
-      </c>
-      <c r="V137" t="n">
-        <v>24.37001542117499</v>
-      </c>
-      <c r="W137" t="n">
-        <v>4.060201325560153</v>
-      </c>
-      <c r="X137" t="n">
-        <v>24.79072301811848</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -10953,18 +9301,6 @@
       <c r="T138" t="n">
         <v>10</v>
       </c>
-      <c r="U138" t="n">
-        <v>3.983488436508413</v>
-      </c>
-      <c r="V138" t="n">
-        <v>15.30885448921041</v>
-      </c>
-      <c r="W138" t="n">
-        <v>3.977962146603917</v>
-      </c>
-      <c r="X138" t="n">
-        <v>15.29291552452456</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -11029,18 +9365,6 @@
       <c r="T139" t="n">
         <v>10</v>
       </c>
-      <c r="U139" t="n">
-        <v>6.075258793424604</v>
-      </c>
-      <c r="V139" t="n">
-        <v>27.91089469290296</v>
-      </c>
-      <c r="W139" t="n">
-        <v>6.102293013312675</v>
-      </c>
-      <c r="X139" t="n">
-        <v>27.64145206022643</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -11105,18 +9429,6 @@
       <c r="T140" t="n">
         <v>10</v>
       </c>
-      <c r="U140" t="n">
-        <v>1.985175854570071</v>
-      </c>
-      <c r="V140" t="n">
-        <v>4.948457385044724</v>
-      </c>
-      <c r="W140" t="n">
-        <v>1.990088629576833</v>
-      </c>
-      <c r="X140" t="n">
-        <v>4.970332478501455</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -11181,18 +9493,6 @@
       <c r="T141" t="n">
         <v>10</v>
       </c>
-      <c r="U141" t="n">
-        <v>0.5002714299390192</v>
-      </c>
-      <c r="V141" t="n">
-        <v>8.12010464919603</v>
-      </c>
-      <c r="W141" t="n">
-        <v>0.5002088322415829</v>
-      </c>
-      <c r="X141" t="n">
-        <v>8.292650913016297</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -11257,18 +9557,6 @@
       <c r="T142" t="n">
         <v>11</v>
       </c>
-      <c r="U142" t="n">
-        <v>1.782637309724038</v>
-      </c>
-      <c r="V142" t="n">
-        <v>4.070951466215316</v>
-      </c>
-      <c r="W142" t="n">
-        <v>1.764582810446823</v>
-      </c>
-      <c r="X142" t="n">
-        <v>3.965974741344458</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -11333,18 +9621,6 @@
       <c r="T143" t="n">
         <v>11</v>
       </c>
-      <c r="U143" t="n">
-        <v>0.4994739791153464</v>
-      </c>
-      <c r="V143" t="n">
-        <v>12.25409018352567</v>
-      </c>
-      <c r="W143" t="n">
-        <v>0.4994780480750728</v>
-      </c>
-      <c r="X143" t="n">
-        <v>12.21743217330932</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -11409,18 +9685,6 @@
       <c r="T144" t="n">
         <v>11</v>
       </c>
-      <c r="U144" t="n">
-        <v>1.783566040397518</v>
-      </c>
-      <c r="V144" t="n">
-        <v>4.534455353826346</v>
-      </c>
-      <c r="W144" t="n">
-        <v>0.500126536756203</v>
-      </c>
-      <c r="X144" t="n">
-        <v>11.41541407922408</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -11485,18 +9749,6 @@
       <c r="T145" t="n">
         <v>10</v>
       </c>
-      <c r="U145" t="n">
-        <v>1.798306804597111</v>
-      </c>
-      <c r="V145" t="n">
-        <v>4.551587074163332</v>
-      </c>
-      <c r="W145" t="n">
-        <v>1.776716722464907</v>
-      </c>
-      <c r="X145" t="n">
-        <v>4.42520359717354</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -11561,18 +9813,6 @@
       <c r="T146" t="n">
         <v>11</v>
       </c>
-      <c r="U146" t="n">
-        <v>1.756657550927369</v>
-      </c>
-      <c r="V146" t="n">
-        <v>4.339071111781656</v>
-      </c>
-      <c r="W146" t="n">
-        <v>1.705247288298402</v>
-      </c>
-      <c r="X146" t="n">
-        <v>4.086405712427184</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -11637,18 +9877,6 @@
       <c r="T147" t="n">
         <v>11</v>
       </c>
-      <c r="U147" t="n">
-        <v>1.812431468985913</v>
-      </c>
-      <c r="V147" t="n">
-        <v>4.566847405156614</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1.756252024585845</v>
-      </c>
-      <c r="X147" t="n">
-        <v>4.286017067401643</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -11713,18 +9941,6 @@
       <c r="T148" t="n">
         <v>11</v>
       </c>
-      <c r="U148" t="n">
-        <v>1.844618668651578</v>
-      </c>
-      <c r="V148" t="n">
-        <v>4.496323218995965</v>
-      </c>
-      <c r="W148" t="n">
-        <v>1.758832570971297</v>
-      </c>
-      <c r="X148" t="n">
-        <v>4.025311740984564</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -11789,18 +10005,6 @@
       <c r="T149" t="n">
         <v>11</v>
       </c>
-      <c r="U149" t="n">
-        <v>1.849763519182318</v>
-      </c>
-      <c r="V149" t="n">
-        <v>4.562531367096986</v>
-      </c>
-      <c r="W149" t="n">
-        <v>1.826229373539494</v>
-      </c>
-      <c r="X149" t="n">
-        <v>4.411168149237721</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -11865,18 +10069,6 @@
       <c r="T150" t="n">
         <v>11</v>
       </c>
-      <c r="U150" t="n">
-        <v>1.863496371140273</v>
-      </c>
-      <c r="V150" t="n">
-        <v>4.721712584369107</v>
-      </c>
-      <c r="W150" t="n">
-        <v>1.860206953601449</v>
-      </c>
-      <c r="X150" t="n">
-        <v>4.678480057588924</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -11941,18 +10133,6 @@
       <c r="T151" t="n">
         <v>12</v>
       </c>
-      <c r="U151" t="n">
-        <v>0.5000083532495857</v>
-      </c>
-      <c r="V151" t="n">
-        <v>24.81593348008018</v>
-      </c>
-      <c r="W151" t="n">
-        <v>0.5000268946269111</v>
-      </c>
-      <c r="X151" t="n">
-        <v>25.21436827065165</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -12017,18 +10197,6 @@
       <c r="T152" t="n">
         <v>11</v>
       </c>
-      <c r="U152" t="n">
-        <v>0.5012164582851361</v>
-      </c>
-      <c r="V152" t="n">
-        <v>3.408776124158301</v>
-      </c>
-      <c r="W152" t="n">
-        <v>0.5014079716915145</v>
-      </c>
-      <c r="X152" t="n">
-        <v>3.342932023220443</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -12093,18 +10261,6 @@
       <c r="T153" t="n">
         <v>11</v>
       </c>
-      <c r="U153" t="n">
-        <v>1.826811112651259</v>
-      </c>
-      <c r="V153" t="n">
-        <v>10.18887811161088</v>
-      </c>
-      <c r="W153" t="n">
-        <v>1.820616679590436</v>
-      </c>
-      <c r="X153" t="n">
-        <v>10.06382213671613</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -12169,18 +10325,6 @@
       <c r="T154" t="n">
         <v>11</v>
       </c>
-      <c r="U154" t="n">
-        <v>1.934486031859329</v>
-      </c>
-      <c r="V154" t="n">
-        <v>30.24232130578817</v>
-      </c>
-      <c r="W154" t="n">
-        <v>1.922852486532305</v>
-      </c>
-      <c r="X154" t="n">
-        <v>30.6593016328754</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -12245,18 +10389,6 @@
       <c r="T155" t="n">
         <v>12</v>
       </c>
-      <c r="U155" t="n">
-        <v>0.5004362916510737</v>
-      </c>
-      <c r="V155" t="n">
-        <v>19.82520761049151</v>
-      </c>
-      <c r="W155" t="n">
-        <v>0.5005183357729605</v>
-      </c>
-      <c r="X155" t="n">
-        <v>19.47812303175221</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -12321,18 +10453,6 @@
       <c r="T156" t="n">
         <v>12</v>
       </c>
-      <c r="U156" t="n">
-        <v>0.5001590333568556</v>
-      </c>
-      <c r="V156" t="n">
-        <v>22.56269530243273</v>
-      </c>
-      <c r="W156" t="n">
-        <v>1.78739016495962</v>
-      </c>
-      <c r="X156" t="n">
-        <v>9.799488976892457</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -12397,18 +10517,6 @@
       <c r="T157" t="n">
         <v>12</v>
       </c>
-      <c r="U157" t="n">
-        <v>0.500260105796087</v>
-      </c>
-      <c r="V157" t="n">
-        <v>21.29605249087464</v>
-      </c>
-      <c r="W157" t="n">
-        <v>0.5002885474506001</v>
-      </c>
-      <c r="X157" t="n">
-        <v>20.77498680219926</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -12473,18 +10581,6 @@
       <c r="T158" t="n">
         <v>12</v>
       </c>
-      <c r="U158" t="n">
-        <v>0.5010652726041858</v>
-      </c>
-      <c r="V158" t="n">
-        <v>17.36945096623379</v>
-      </c>
-      <c r="W158" t="n">
-        <v>0.5015518093157035</v>
-      </c>
-      <c r="X158" t="n">
-        <v>16.66013063621873</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -12549,18 +10645,6 @@
       <c r="T159" t="n">
         <v>12</v>
       </c>
-      <c r="U159" t="n">
-        <v>0.5003539760564792</v>
-      </c>
-      <c r="V159" t="n">
-        <v>21.71859630124463</v>
-      </c>
-      <c r="W159" t="n">
-        <v>1.884399510832024</v>
-      </c>
-      <c r="X159" t="n">
-        <v>5.064585558166473</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -12625,18 +10709,6 @@
       <c r="T160" t="n">
         <v>12</v>
       </c>
-      <c r="U160" t="n">
-        <v>0.4999919475872526</v>
-      </c>
-      <c r="V160" t="n">
-        <v>25.34165121650276</v>
-      </c>
-      <c r="W160" t="n">
-        <v>0.4999057399755182</v>
-      </c>
-      <c r="X160" t="n">
-        <v>23.87610997482277</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -12701,18 +10773,6 @@
       <c r="T161" t="n">
         <v>12</v>
       </c>
-      <c r="U161" t="n">
-        <v>2.005593165958929</v>
-      </c>
-      <c r="V161" t="n">
-        <v>4.833750888722696</v>
-      </c>
-      <c r="W161" t="n">
-        <v>3.321116811718548</v>
-      </c>
-      <c r="X161" t="n">
-        <v>5.384599704529626</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -12777,18 +10837,6 @@
       <c r="T162" t="n">
         <v>12</v>
       </c>
-      <c r="U162" t="n">
-        <v>3.29391685424905</v>
-      </c>
-      <c r="V162" t="n">
-        <v>5.488489536795902</v>
-      </c>
-      <c r="W162" t="n">
-        <v>3.652835815030503</v>
-      </c>
-      <c r="X162" t="n">
-        <v>7.515661052676113</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -12853,18 +10901,6 @@
       <c r="T163" t="n">
         <v>11</v>
       </c>
-      <c r="U163" t="n">
-        <v>1.981062056327822</v>
-      </c>
-      <c r="V163" t="n">
-        <v>4.983658247513872</v>
-      </c>
-      <c r="W163" t="n">
-        <v>1.977910894321577</v>
-      </c>
-      <c r="X163" t="n">
-        <v>4.99478246753943</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -12929,18 +10965,6 @@
       <c r="T164" t="n">
         <v>11</v>
       </c>
-      <c r="U164" t="n">
-        <v>1.986523476739483</v>
-      </c>
-      <c r="V164" t="n">
-        <v>29.73542059384774</v>
-      </c>
-      <c r="W164" t="n">
-        <v>1.981819274993009</v>
-      </c>
-      <c r="X164" t="n">
-        <v>29.91421884702215</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -13005,18 +11029,6 @@
       <c r="T165" t="n">
         <v>11</v>
       </c>
-      <c r="U165" t="n">
-        <v>1.945136439423093</v>
-      </c>
-      <c r="V165" t="n">
-        <v>15.00060133877988</v>
-      </c>
-      <c r="W165" t="n">
-        <v>1.91429985520092</v>
-      </c>
-      <c r="X165" t="n">
-        <v>10.05207275542819</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -13081,18 +11093,6 @@
       <c r="T166" t="n">
         <v>11</v>
       </c>
-      <c r="U166" t="n">
-        <v>1.938135671618367</v>
-      </c>
-      <c r="V166" t="n">
-        <v>30.32298337415708</v>
-      </c>
-      <c r="W166" t="n">
-        <v>1.916275244556704</v>
-      </c>
-      <c r="X166" t="n">
-        <v>15.26977087539969</v>
-      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -13157,18 +11157,6 @@
       <c r="T167" t="n">
         <v>11</v>
       </c>
-      <c r="U167" t="n">
-        <v>1.939316181707153</v>
-      </c>
-      <c r="V167" t="n">
-        <v>29.8424809985558</v>
-      </c>
-      <c r="W167" t="n">
-        <v>1.917296153928757</v>
-      </c>
-      <c r="X167" t="n">
-        <v>14.99549324791231</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -13233,18 +11221,6 @@
       <c r="T168" t="n">
         <v>11</v>
       </c>
-      <c r="U168" t="n">
-        <v>1.90495051142541</v>
-      </c>
-      <c r="V168" t="n">
-        <v>30.61200700781404</v>
-      </c>
-      <c r="W168" t="n">
-        <v>1.905494790416828</v>
-      </c>
-      <c r="X168" t="n">
-        <v>30.5401053956293</v>
-      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -13309,18 +11285,6 @@
       <c r="T169" t="n">
         <v>11</v>
       </c>
-      <c r="U169" t="n">
-        <v>1.933660526181091</v>
-      </c>
-      <c r="V169" t="n">
-        <v>4.961643334964025</v>
-      </c>
-      <c r="W169" t="n">
-        <v>1.924691146196533</v>
-      </c>
-      <c r="X169" t="n">
-        <v>4.92282527007182</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -13385,18 +11349,6 @@
       <c r="T170" t="n">
         <v>11</v>
       </c>
-      <c r="U170" t="n">
-        <v>1.957979638819162</v>
-      </c>
-      <c r="V170" t="n">
-        <v>5.013316218384514</v>
-      </c>
-      <c r="W170" t="n">
-        <v>1.908235553953708</v>
-      </c>
-      <c r="X170" t="n">
-        <v>25.6453481196475</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -13461,18 +11413,6 @@
       <c r="T171" t="n">
         <v>11</v>
       </c>
-      <c r="U171" t="n">
-        <v>1.90267482804282</v>
-      </c>
-      <c r="V171" t="n">
-        <v>24.99212391472446</v>
-      </c>
-      <c r="W171" t="n">
-        <v>1.878452982880018</v>
-      </c>
-      <c r="X171" t="n">
-        <v>15.1210719110525</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -13537,18 +11477,6 @@
       <c r="T172" t="n">
         <v>11</v>
       </c>
-      <c r="U172" t="n">
-        <v>1.931513820743582</v>
-      </c>
-      <c r="V172" t="n">
-        <v>4.977600264521925</v>
-      </c>
-      <c r="W172" t="n">
-        <v>1.877983429406659</v>
-      </c>
-      <c r="X172" t="n">
-        <v>26.28296207860643</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -13613,18 +11541,6 @@
       <c r="T173" t="n">
         <v>11</v>
       </c>
-      <c r="U173" t="n">
-        <v>1.8810628719245</v>
-      </c>
-      <c r="V173" t="n">
-        <v>31.30786659781027</v>
-      </c>
-      <c r="W173" t="n">
-        <v>1.865825688549793</v>
-      </c>
-      <c r="X173" t="n">
-        <v>26.32754641902401</v>
-      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -13689,18 +11605,6 @@
       <c r="T174" t="n">
         <v>11</v>
       </c>
-      <c r="U174" t="n">
-        <v>1.892798046999406</v>
-      </c>
-      <c r="V174" t="n">
-        <v>30.08548174882626</v>
-      </c>
-      <c r="W174" t="n">
-        <v>1.882687030305224</v>
-      </c>
-      <c r="X174" t="n">
-        <v>30.34435996398286</v>
-      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -13765,18 +11669,6 @@
       <c r="T175" t="n">
         <v>11</v>
       </c>
-      <c r="U175" t="n">
-        <v>1.899673377719128</v>
-      </c>
-      <c r="V175" t="n">
-        <v>28.87782566136226</v>
-      </c>
-      <c r="W175" t="n">
-        <v>1.895034413490458</v>
-      </c>
-      <c r="X175" t="n">
-        <v>29.03784797115214</v>
-      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -13841,18 +11733,6 @@
       <c r="T176" t="n">
         <v>11</v>
       </c>
-      <c r="U176" t="n">
-        <v>1.99001360936166</v>
-      </c>
-      <c r="V176" t="n">
-        <v>27.63587814389664</v>
-      </c>
-      <c r="W176" t="n">
-        <v>1.989352969242566</v>
-      </c>
-      <c r="X176" t="n">
-        <v>27.6113728972215</v>
-      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -13917,18 +11797,6 @@
       <c r="T177" t="n">
         <v>11</v>
       </c>
-      <c r="U177" t="n">
-        <v>1.999929629411173</v>
-      </c>
-      <c r="V177" t="n">
-        <v>28.24300428617826</v>
-      </c>
-      <c r="W177" t="n">
-        <v>1.998206689305153</v>
-      </c>
-      <c r="X177" t="n">
-        <v>28.22446590641684</v>
-      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -13993,18 +11861,6 @@
       <c r="T178" t="n">
         <v>11</v>
       </c>
-      <c r="U178" t="n">
-        <v>2.023669065340907</v>
-      </c>
-      <c r="V178" t="n">
-        <v>10.5411375246947</v>
-      </c>
-      <c r="W178" t="n">
-        <v>2.02972899663414</v>
-      </c>
-      <c r="X178" t="n">
-        <v>10.53791044088348</v>
-      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -14069,18 +11925,6 @@
       <c r="T179" t="n">
         <v>11</v>
       </c>
-      <c r="U179" t="n">
-        <v>2.074084089879702</v>
-      </c>
-      <c r="V179" t="n">
-        <v>24.71828445249393</v>
-      </c>
-      <c r="W179" t="n">
-        <v>3.237124680228828</v>
-      </c>
-      <c r="X179" t="n">
-        <v>5.700797528368616</v>
-      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -14145,18 +11989,6 @@
       <c r="T180" t="n">
         <v>11</v>
       </c>
-      <c r="U180" t="n">
-        <v>3.379319209723735</v>
-      </c>
-      <c r="V180" t="n">
-        <v>5.655833574498778</v>
-      </c>
-      <c r="W180" t="n">
-        <v>3.341288631361821</v>
-      </c>
-      <c r="X180" t="n">
-        <v>5.667487817586321</v>
-      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -14221,18 +12053,6 @@
       <c r="T181" t="n">
         <v>11</v>
       </c>
-      <c r="U181" t="n">
-        <v>3.409564011101403</v>
-      </c>
-      <c r="V181" t="n">
-        <v>5.565431397537747</v>
-      </c>
-      <c r="W181" t="n">
-        <v>3.377337885774456</v>
-      </c>
-      <c r="X181" t="n">
-        <v>5.604640865325169</v>
-      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -14297,18 +12117,6 @@
       <c r="T182" t="n">
         <v>11</v>
       </c>
-      <c r="U182" t="n">
-        <v>2.043630343560175</v>
-      </c>
-      <c r="V182" t="n">
-        <v>4.710345543097089</v>
-      </c>
-      <c r="W182" t="n">
-        <v>3.263236749614817</v>
-      </c>
-      <c r="X182" t="n">
-        <v>5.544475484780997</v>
-      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -14373,18 +12181,6 @@
       <c r="T183" t="n">
         <v>11</v>
       </c>
-      <c r="U183" t="n">
-        <v>2.043438760401905</v>
-      </c>
-      <c r="V183" t="n">
-        <v>4.716254842755112</v>
-      </c>
-      <c r="W183" t="n">
-        <v>2.057459244622859</v>
-      </c>
-      <c r="X183" t="n">
-        <v>4.645934668560758</v>
-      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -14449,18 +12245,6 @@
       <c r="T184" t="n">
         <v>11</v>
       </c>
-      <c r="U184" t="n">
-        <v>2.009916066653742</v>
-      </c>
-      <c r="V184" t="n">
-        <v>4.920088039250317</v>
-      </c>
-      <c r="W184" t="n">
-        <v>2.033953615511784</v>
-      </c>
-      <c r="X184" t="n">
-        <v>30.1066524304629</v>
-      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -14525,18 +12309,6 @@
       <c r="T185" t="n">
         <v>11</v>
       </c>
-      <c r="U185" t="n">
-        <v>2.016493915901671</v>
-      </c>
-      <c r="V185" t="n">
-        <v>4.763971044345168</v>
-      </c>
-      <c r="W185" t="n">
-        <v>2.014628354215912</v>
-      </c>
-      <c r="X185" t="n">
-        <v>4.784231282086604</v>
-      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -14601,18 +12373,6 @@
       <c r="T186" t="n">
         <v>11</v>
       </c>
-      <c r="U186" t="n">
-        <v>2.002918872143243</v>
-      </c>
-      <c r="V186" t="n">
-        <v>4.775647454135735</v>
-      </c>
-      <c r="W186" t="n">
-        <v>1.994947737470242</v>
-      </c>
-      <c r="X186" t="n">
-        <v>4.817086626295629</v>
-      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -14677,18 +12437,6 @@
       <c r="T187" t="n">
         <v>11</v>
       </c>
-      <c r="U187" t="n">
-        <v>2.01131955361873</v>
-      </c>
-      <c r="V187" t="n">
-        <v>4.764863140100497</v>
-      </c>
-      <c r="W187" t="n">
-        <v>2.010192503947848</v>
-      </c>
-      <c r="X187" t="n">
-        <v>4.794588812324752</v>
-      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -14753,18 +12501,6 @@
       <c r="T188" t="n">
         <v>11</v>
       </c>
-      <c r="U188" t="n">
-        <v>2.034190034177415</v>
-      </c>
-      <c r="V188" t="n">
-        <v>4.505906137778768</v>
-      </c>
-      <c r="W188" t="n">
-        <v>2.033496035238657</v>
-      </c>
-      <c r="X188" t="n">
-        <v>4.518462628750046</v>
-      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -14829,18 +12565,6 @@
       <c r="T189" t="n">
         <v>11</v>
       </c>
-      <c r="U189" t="n">
-        <v>2.021109938019107</v>
-      </c>
-      <c r="V189" t="n">
-        <v>4.593883904413615</v>
-      </c>
-      <c r="W189" t="n">
-        <v>2.009669671043396</v>
-      </c>
-      <c r="X189" t="n">
-        <v>4.647770729803462</v>
-      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -14905,18 +12629,6 @@
       <c r="T190" t="n">
         <v>11</v>
       </c>
-      <c r="U190" t="n">
-        <v>2.046111556265463</v>
-      </c>
-      <c r="V190" t="n">
-        <v>4.40376768070984</v>
-      </c>
-      <c r="W190" t="n">
-        <v>2.044263714233865</v>
-      </c>
-      <c r="X190" t="n">
-        <v>4.410954925889269</v>
-      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -14981,18 +12693,6 @@
       <c r="T191" t="n">
         <v>11</v>
       </c>
-      <c r="U191" t="n">
-        <v>2.051672372921916</v>
-      </c>
-      <c r="V191" t="n">
-        <v>4.315844525591556</v>
-      </c>
-      <c r="W191" t="n">
-        <v>2.047619229237958</v>
-      </c>
-      <c r="X191" t="n">
-        <v>4.326575184011466</v>
-      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -15057,18 +12757,6 @@
       <c r="T192" t="n">
         <v>11</v>
       </c>
-      <c r="U192" t="n">
-        <v>2.033314683004546</v>
-      </c>
-      <c r="V192" t="n">
-        <v>4.472870665611549</v>
-      </c>
-      <c r="W192" t="n">
-        <v>2.020319277595334</v>
-      </c>
-      <c r="X192" t="n">
-        <v>4.515141751828486</v>
-      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -15133,18 +12821,6 @@
       <c r="T193" t="n">
         <v>11</v>
       </c>
-      <c r="U193" t="n">
-        <v>2.027840460451042</v>
-      </c>
-      <c r="V193" t="n">
-        <v>4.627070891047321</v>
-      </c>
-      <c r="W193" t="n">
-        <v>2.009732632534604</v>
-      </c>
-      <c r="X193" t="n">
-        <v>4.693423824988357</v>
-      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -15209,18 +12885,6 @@
       <c r="T194" t="n">
         <v>11</v>
       </c>
-      <c r="U194" t="n">
-        <v>2.041656240918573</v>
-      </c>
-      <c r="V194" t="n">
-        <v>4.424014973748717</v>
-      </c>
-      <c r="W194" t="n">
-        <v>2.054209946470362</v>
-      </c>
-      <c r="X194" t="n">
-        <v>4.346850023406977</v>
-      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -15285,18 +12949,6 @@
       <c r="T195" t="n">
         <v>11</v>
       </c>
-      <c r="U195" t="n">
-        <v>2.046605584270801</v>
-      </c>
-      <c r="V195" t="n">
-        <v>4.297116382791296</v>
-      </c>
-      <c r="W195" t="n">
-        <v>2.047520223580387</v>
-      </c>
-      <c r="X195" t="n">
-        <v>4.270667321972059</v>
-      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -15361,18 +13013,6 @@
       <c r="T196" t="n">
         <v>11</v>
       </c>
-      <c r="U196" t="n">
-        <v>2.056984911633684</v>
-      </c>
-      <c r="V196" t="n">
-        <v>4.272625550122306</v>
-      </c>
-      <c r="W196" t="n">
-        <v>2.05760335634917</v>
-      </c>
-      <c r="X196" t="n">
-        <v>4.265419981083037</v>
-      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -15437,18 +13077,6 @@
       <c r="T197" t="n">
         <v>10</v>
       </c>
-      <c r="U197" t="n">
-        <v>2.046875178279739</v>
-      </c>
-      <c r="V197" t="n">
-        <v>4.369064591644996</v>
-      </c>
-      <c r="W197" t="n">
-        <v>2.045718857725022</v>
-      </c>
-      <c r="X197" t="n">
-        <v>4.372161431048758</v>
-      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -15513,18 +13141,6 @@
       <c r="T198" t="n">
         <v>10</v>
       </c>
-      <c r="U198" t="n">
-        <v>3.842119372717041</v>
-      </c>
-      <c r="V198" t="n">
-        <v>12.23627425115593</v>
-      </c>
-      <c r="W198" t="n">
-        <v>2.062174156375678</v>
-      </c>
-      <c r="X198" t="n">
-        <v>4.172483113228613</v>
-      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -15589,18 +13205,6 @@
       <c r="T199" t="n">
         <v>10</v>
       </c>
-      <c r="U199" t="n">
-        <v>4.198440108591448</v>
-      </c>
-      <c r="V199" t="n">
-        <v>26.31111657272676</v>
-      </c>
-      <c r="W199" t="n">
-        <v>4.212731657313366</v>
-      </c>
-      <c r="X199" t="n">
-        <v>26.14611854560261</v>
-      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -15665,18 +13269,6 @@
       <c r="T200" t="n">
         <v>10</v>
       </c>
-      <c r="U200" t="n">
-        <v>4.126660229249758</v>
-      </c>
-      <c r="V200" t="n">
-        <v>26.80008884445099</v>
-      </c>
-      <c r="W200" t="n">
-        <v>4.168028517747504</v>
-      </c>
-      <c r="X200" t="n">
-        <v>27.0443440880887</v>
-      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -15741,18 +13333,6 @@
       <c r="T201" t="n">
         <v>10</v>
       </c>
-      <c r="U201" t="n">
-        <v>5.497378075912438</v>
-      </c>
-      <c r="V201" t="n">
-        <v>24.4261604876516</v>
-      </c>
-      <c r="W201" t="n">
-        <v>5.556864463333384</v>
-      </c>
-      <c r="X201" t="n">
-        <v>24.68581081176901</v>
-      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -15817,18 +13397,6 @@
       <c r="T202" t="n">
         <v>10</v>
       </c>
-      <c r="U202" t="n">
-        <v>4.220564007034175</v>
-      </c>
-      <c r="V202" t="n">
-        <v>26.54314350927975</v>
-      </c>
-      <c r="W202" t="n">
-        <v>5.433595611398027</v>
-      </c>
-      <c r="X202" t="n">
-        <v>19.48515231285298</v>
-      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -15893,18 +13461,6 @@
       <c r="T203" t="n">
         <v>10</v>
       </c>
-      <c r="U203" t="n">
-        <v>3.837323187647061</v>
-      </c>
-      <c r="V203" t="n">
-        <v>12.56287077547621</v>
-      </c>
-      <c r="W203" t="n">
-        <v>3.820313574429116</v>
-      </c>
-      <c r="X203" t="n">
-        <v>12.45058363445481</v>
-      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -15969,18 +13525,6 @@
       <c r="T204" t="n">
         <v>10</v>
       </c>
-      <c r="U204" t="n">
-        <v>2.062252819957949</v>
-      </c>
-      <c r="V204" t="n">
-        <v>4.27991165425509</v>
-      </c>
-      <c r="W204" t="n">
-        <v>2.063946255314191</v>
-      </c>
-      <c r="X204" t="n">
-        <v>4.271636988814503</v>
-      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -16045,18 +13589,6 @@
       <c r="T205" t="n">
         <v>10</v>
       </c>
-      <c r="U205" t="n">
-        <v>3.96156341839077</v>
-      </c>
-      <c r="V205" t="n">
-        <v>13.10631699891785</v>
-      </c>
-      <c r="W205" t="n">
-        <v>3.904542280809681</v>
-      </c>
-      <c r="X205" t="n">
-        <v>16.59321143036802</v>
-      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -16121,18 +13653,6 @@
       <c r="T206" t="n">
         <v>11</v>
       </c>
-      <c r="U206" t="n">
-        <v>0.5002069483938743</v>
-      </c>
-      <c r="V206" t="n">
-        <v>21.64386417101076</v>
-      </c>
-      <c r="W206" t="n">
-        <v>0.5001199726744472</v>
-      </c>
-      <c r="X206" t="n">
-        <v>21.67546350233059</v>
-      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -16197,18 +13717,6 @@
       <c r="T207" t="n">
         <v>11</v>
       </c>
-      <c r="U207" t="n">
-        <v>3.816910548065823</v>
-      </c>
-      <c r="V207" t="n">
-        <v>16.40963869287152</v>
-      </c>
-      <c r="W207" t="n">
-        <v>3.691522283635851</v>
-      </c>
-      <c r="X207" t="n">
-        <v>20.56817805923973</v>
-      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -16273,18 +13781,6 @@
       <c r="T208" t="n">
         <v>11</v>
       </c>
-      <c r="U208" t="n">
-        <v>3.914487694770616</v>
-      </c>
-      <c r="V208" t="n">
-        <v>12.48747751546517</v>
-      </c>
-      <c r="W208" t="n">
-        <v>2.060138071201726</v>
-      </c>
-      <c r="X208" t="n">
-        <v>4.228472678213128</v>
-      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -16349,18 +13845,6 @@
       <c r="T209" t="n">
         <v>11</v>
       </c>
-      <c r="U209" t="n">
-        <v>2.054081881818002</v>
-      </c>
-      <c r="V209" t="n">
-        <v>4.347316901697276</v>
-      </c>
-      <c r="W209" t="n">
-        <v>2.052298718337896</v>
-      </c>
-      <c r="X209" t="n">
-        <v>4.341641507811409</v>
-      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -16425,18 +13909,6 @@
       <c r="T210" t="n">
         <v>10</v>
       </c>
-      <c r="U210" t="n">
-        <v>2.046816459957293</v>
-      </c>
-      <c r="V210" t="n">
-        <v>4.358945397517669</v>
-      </c>
-      <c r="W210" t="n">
-        <v>2.045071860649683</v>
-      </c>
-      <c r="X210" t="n">
-        <v>4.350202697791212</v>
-      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -16501,18 +13973,6 @@
       <c r="T211" t="n">
         <v>10</v>
       </c>
-      <c r="U211" t="n">
-        <v>2.043901548988741</v>
-      </c>
-      <c r="V211" t="n">
-        <v>4.37546259592222</v>
-      </c>
-      <c r="W211" t="n">
-        <v>0.5002699079398105</v>
-      </c>
-      <c r="X211" t="n">
-        <v>21.4262681109331</v>
-      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -16577,18 +14037,6 @@
       <c r="T212" t="n">
         <v>10</v>
       </c>
-      <c r="U212" t="n">
-        <v>2.017491066858051</v>
-      </c>
-      <c r="V212" t="n">
-        <v>4.66322406598711</v>
-      </c>
-      <c r="W212" t="n">
-        <v>0.5007093701711259</v>
-      </c>
-      <c r="X212" t="n">
-        <v>19.33972545776808</v>
-      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -16653,18 +14101,6 @@
       <c r="T213" t="n">
         <v>10</v>
       </c>
-      <c r="U213" t="n">
-        <v>2.047405933093935</v>
-      </c>
-      <c r="V213" t="n">
-        <v>4.441930979375663</v>
-      </c>
-      <c r="W213" t="n">
-        <v>2.046355684163108</v>
-      </c>
-      <c r="X213" t="n">
-        <v>4.437724898265825</v>
-      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -16729,18 +14165,6 @@
       <c r="T214" t="n">
         <v>10</v>
       </c>
-      <c r="U214" t="n">
-        <v>2.035750365927959</v>
-      </c>
-      <c r="V214" t="n">
-        <v>4.550783857701205</v>
-      </c>
-      <c r="W214" t="n">
-        <v>2.031701962776762</v>
-      </c>
-      <c r="X214" t="n">
-        <v>4.551512009410563</v>
-      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -16805,18 +14229,6 @@
       <c r="T215" t="n">
         <v>10</v>
       </c>
-      <c r="U215" t="n">
-        <v>2.033725598392745</v>
-      </c>
-      <c r="V215" t="n">
-        <v>4.4968651530133</v>
-      </c>
-      <c r="W215" t="n">
-        <v>2.028821980746603</v>
-      </c>
-      <c r="X215" t="n">
-        <v>4.497857124220407</v>
-      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -16881,18 +14293,6 @@
       <c r="T216" t="n">
         <v>10</v>
       </c>
-      <c r="U216" t="n">
-        <v>2.039208024826578</v>
-      </c>
-      <c r="V216" t="n">
-        <v>4.564902222618127</v>
-      </c>
-      <c r="W216" t="n">
-        <v>2.037968906032987</v>
-      </c>
-      <c r="X216" t="n">
-        <v>4.541960480230118</v>
-      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -16957,18 +14357,6 @@
       <c r="T217" t="n">
         <v>10</v>
       </c>
-      <c r="U217" t="n">
-        <v>2.02612726483566</v>
-      </c>
-      <c r="V217" t="n">
-        <v>4.608066905512912</v>
-      </c>
-      <c r="W217" t="n">
-        <v>0.5005952360462902</v>
-      </c>
-      <c r="X217" t="n">
-        <v>19.9570576493137</v>
-      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -17033,18 +14421,6 @@
       <c r="T218" t="n">
         <v>10</v>
       </c>
-      <c r="U218" t="n">
-        <v>0.5010297708988823</v>
-      </c>
-      <c r="V218" t="n">
-        <v>15.45539897513081</v>
-      </c>
-      <c r="W218" t="n">
-        <v>0.5012900485033147</v>
-      </c>
-      <c r="X218" t="n">
-        <v>16.47024456111835</v>
-      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -17109,18 +14485,6 @@
       <c r="T219" t="n">
         <v>10</v>
       </c>
-      <c r="U219" t="n">
-        <v>2.014304665921843</v>
-      </c>
-      <c r="V219" t="n">
-        <v>26.51226985761071</v>
-      </c>
-      <c r="W219" t="n">
-        <v>2.002336693302797</v>
-      </c>
-      <c r="X219" t="n">
-        <v>26.70712709277815</v>
-      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -17185,18 +14549,6 @@
       <c r="T220" t="n">
         <v>10</v>
       </c>
-      <c r="U220" t="n">
-        <v>2.017893116286202</v>
-      </c>
-      <c r="V220" t="n">
-        <v>4.827019687101629</v>
-      </c>
-      <c r="W220" t="n">
-        <v>0.500449324687687</v>
-      </c>
-      <c r="X220" t="n">
-        <v>17.2706219872735</v>
-      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -17261,18 +14613,6 @@
       <c r="T221" t="n">
         <v>10</v>
       </c>
-      <c r="U221" t="n">
-        <v>2.009977360545327</v>
-      </c>
-      <c r="V221" t="n">
-        <v>26.06775634157907</v>
-      </c>
-      <c r="W221" t="n">
-        <v>1.994630469619121</v>
-      </c>
-      <c r="X221" t="n">
-        <v>26.27068907685309</v>
-      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -17337,18 +14677,6 @@
       <c r="T222" t="n">
         <v>10</v>
       </c>
-      <c r="U222" t="n">
-        <v>2.032292833521638</v>
-      </c>
-      <c r="V222" t="n">
-        <v>4.657703997461106</v>
-      </c>
-      <c r="W222" t="n">
-        <v>2.0270092257779</v>
-      </c>
-      <c r="X222" t="n">
-        <v>4.690241472516276</v>
-      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -17413,18 +14741,6 @@
       <c r="T223" t="n">
         <v>11</v>
       </c>
-      <c r="U223" t="n">
-        <v>2.041070212995902</v>
-      </c>
-      <c r="V223" t="n">
-        <v>4.50196572434218</v>
-      </c>
-      <c r="W223" t="n">
-        <v>0.5000768448851843</v>
-      </c>
-      <c r="X223" t="n">
-        <v>19.53459109125441</v>
-      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -17489,18 +14805,6 @@
       <c r="T224" t="n">
         <v>11</v>
       </c>
-      <c r="U224" t="n">
-        <v>0.5004061283985127</v>
-      </c>
-      <c r="V224" t="n">
-        <v>20.17533700815577</v>
-      </c>
-      <c r="W224" t="n">
-        <v>0.5005329217480262</v>
-      </c>
-      <c r="X224" t="n">
-        <v>19.68364481922004</v>
-      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -17565,18 +14869,6 @@
       <c r="T225" t="n">
         <v>11</v>
       </c>
-      <c r="U225" t="n">
-        <v>4.006944026873827</v>
-      </c>
-      <c r="V225" t="n">
-        <v>22.06039069471922</v>
-      </c>
-      <c r="W225" t="n">
-        <v>3.961643377432522</v>
-      </c>
-      <c r="X225" t="n">
-        <v>21.56135786181873</v>
-      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -17641,18 +14933,6 @@
       <c r="T226" t="n">
         <v>10</v>
       </c>
-      <c r="U226" t="n">
-        <v>0.5037297284059441</v>
-      </c>
-      <c r="V226" t="n">
-        <v>2.922285239160153</v>
-      </c>
-      <c r="W226" t="n">
-        <v>0.503669982844227</v>
-      </c>
-      <c r="X226" t="n">
-        <v>2.899218874151479</v>
-      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -17717,18 +14997,6 @@
       <c r="T227" t="n">
         <v>11</v>
       </c>
-      <c r="U227" t="n">
-        <v>4.009502060931565</v>
-      </c>
-      <c r="V227" t="n">
-        <v>24.25339683897448</v>
-      </c>
-      <c r="W227" t="n">
-        <v>4.024569895202172</v>
-      </c>
-      <c r="X227" t="n">
-        <v>24.68293198615718</v>
-      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -17793,18 +15061,6 @@
       <c r="T228" t="n">
         <v>11</v>
       </c>
-      <c r="U228" t="n">
-        <v>5.929196246868795</v>
-      </c>
-      <c r="V228" t="n">
-        <v>22.56521873601041</v>
-      </c>
-      <c r="W228" t="n">
-        <v>5.935202824784031</v>
-      </c>
-      <c r="X228" t="n">
-        <v>24.20664403143461</v>
-      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -17869,18 +15125,6 @@
       <c r="T229" t="n">
         <v>10</v>
       </c>
-      <c r="U229" t="n">
-        <v>5.668148128091246</v>
-      </c>
-      <c r="V229" t="n">
-        <v>23.18035722891852</v>
-      </c>
-      <c r="W229" t="n">
-        <v>5.691493374804374</v>
-      </c>
-      <c r="X229" t="n">
-        <v>23.44246558101363</v>
-      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -17945,18 +15189,6 @@
       <c r="T230" t="n">
         <v>10</v>
       </c>
-      <c r="U230" t="n">
-        <v>3.821016700170529</v>
-      </c>
-      <c r="V230" t="n">
-        <v>15.24457143331163</v>
-      </c>
-      <c r="W230" t="n">
-        <v>3.808980939605918</v>
-      </c>
-      <c r="X230" t="n">
-        <v>15.15810312217764</v>
-      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -18021,18 +15253,6 @@
       <c r="T231" t="n">
         <v>10</v>
       </c>
-      <c r="U231" t="n">
-        <v>3.87638305469502</v>
-      </c>
-      <c r="V231" t="n">
-        <v>11.22689205516747</v>
-      </c>
-      <c r="W231" t="n">
-        <v>2.034285845702777</v>
-      </c>
-      <c r="X231" t="n">
-        <v>4.48686341961488</v>
-      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -18097,18 +15317,6 @@
       <c r="T232" t="n">
         <v>10</v>
       </c>
-      <c r="U232" t="n">
-        <v>3.66011595233805</v>
-      </c>
-      <c r="V232" t="n">
-        <v>5.280390416545423</v>
-      </c>
-      <c r="W232" t="n">
-        <v>2.03469476082327</v>
-      </c>
-      <c r="X232" t="n">
-        <v>4.54404937871993</v>
-      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -18173,18 +15381,6 @@
       <c r="T233" t="n">
         <v>11</v>
       </c>
-      <c r="U233" t="n">
-        <v>2.024013762538235</v>
-      </c>
-      <c r="V233" t="n">
-        <v>4.646907533250768</v>
-      </c>
-      <c r="W233" t="n">
-        <v>2.024605860427415</v>
-      </c>
-      <c r="X233" t="n">
-        <v>4.627117280655034</v>
-      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -18249,18 +15445,6 @@
       <c r="T234" t="n">
         <v>11</v>
       </c>
-      <c r="U234" t="n">
-        <v>2.032137645176289</v>
-      </c>
-      <c r="V234" t="n">
-        <v>4.486423872065129</v>
-      </c>
-      <c r="W234" t="n">
-        <v>2.034393822552682</v>
-      </c>
-      <c r="X234" t="n">
-        <v>4.440216168687756</v>
-      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -18325,18 +15509,6 @@
       <c r="T235" t="n">
         <v>11</v>
       </c>
-      <c r="U235" t="n">
-        <v>0.4994430241197332</v>
-      </c>
-      <c r="V235" t="n">
-        <v>21.28450919047522</v>
-      </c>
-      <c r="W235" t="n">
-        <v>0.4993609059210503</v>
-      </c>
-      <c r="X235" t="n">
-        <v>21.00279999265247</v>
-      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -18401,18 +15573,6 @@
       <c r="T236" t="n">
         <v>11</v>
       </c>
-      <c r="U236" t="n">
-        <v>0.4994666421539731</v>
-      </c>
-      <c r="V236" t="n">
-        <v>23.44458047209885</v>
-      </c>
-      <c r="W236" t="n">
-        <v>0.4993895696669655</v>
-      </c>
-      <c r="X236" t="n">
-        <v>23.87517675699474</v>
-      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -18477,18 +15637,6 @@
       <c r="T237" t="n">
         <v>11</v>
       </c>
-      <c r="U237" t="n">
-        <v>0.499538059842457</v>
-      </c>
-      <c r="V237" t="n">
-        <v>24.36378977374341</v>
-      </c>
-      <c r="W237" t="n">
-        <v>0.4994368862686701</v>
-      </c>
-      <c r="X237" t="n">
-        <v>24.97785438864733</v>
-      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -18553,18 +15701,6 @@
       <c r="T238" t="n">
         <v>11</v>
       </c>
-      <c r="U238" t="n">
-        <v>2.01826439075618</v>
-      </c>
-      <c r="V238" t="n">
-        <v>4.58520513533839</v>
-      </c>
-      <c r="W238" t="n">
-        <v>2.01719648018065</v>
-      </c>
-      <c r="X238" t="n">
-        <v>4.574390033173598</v>
-      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -18629,18 +15765,6 @@
       <c r="T239" t="n">
         <v>11</v>
       </c>
-      <c r="U239" t="n">
-        <v>5.973230879148425</v>
-      </c>
-      <c r="V239" t="n">
-        <v>25.97335967036804</v>
-      </c>
-      <c r="W239" t="n">
-        <v>6.005049747885092</v>
-      </c>
-      <c r="X239" t="n">
-        <v>26.24353585622212</v>
-      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -18705,18 +15829,6 @@
       <c r="T240" t="n">
         <v>11</v>
       </c>
-      <c r="U240" t="n">
-        <v>0.5002362536767385</v>
-      </c>
-      <c r="V240" t="n">
-        <v>3.428007266290538</v>
-      </c>
-      <c r="W240" t="n">
-        <v>0.5001540857644349</v>
-      </c>
-      <c r="X240" t="n">
-        <v>3.379810208611864</v>
-      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -18781,18 +15893,6 @@
       <c r="T241" t="n">
         <v>11</v>
       </c>
-      <c r="U241" t="n">
-        <v>0.4995935838556234</v>
-      </c>
-      <c r="V241" t="n">
-        <v>20.08252411768824</v>
-      </c>
-      <c r="W241" t="n">
-        <v>0.499546713399447</v>
-      </c>
-      <c r="X241" t="n">
-        <v>21.13208627629192</v>
-      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -18857,18 +15957,6 @@
       <c r="T242" t="n">
         <v>11</v>
       </c>
-      <c r="U242" t="n">
-        <v>3.88042535111362</v>
-      </c>
-      <c r="V242" t="n">
-        <v>11.00747920136771</v>
-      </c>
-      <c r="W242" t="n">
-        <v>3.869709929564704</v>
-      </c>
-      <c r="X242" t="n">
-        <v>11.03654000755452</v>
-      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -18933,18 +16021,6 @@
       <c r="T243" t="n">
         <v>11</v>
       </c>
-      <c r="U243" t="n">
-        <v>0.499655103069235</v>
-      </c>
-      <c r="V243" t="n">
-        <v>25.158621108655</v>
-      </c>
-      <c r="W243" t="n">
-        <v>0.4995189287851442</v>
-      </c>
-      <c r="X243" t="n">
-        <v>25.18154857170488</v>
-      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -19009,18 +16085,6 @@
       <c r="T244" t="n">
         <v>12</v>
       </c>
-      <c r="U244" t="n">
-        <v>2.012302592160973</v>
-      </c>
-      <c r="V244" t="n">
-        <v>4.720704801382672</v>
-      </c>
-      <c r="W244" t="n">
-        <v>0.4999442389080686</v>
-      </c>
-      <c r="X244" t="n">
-        <v>26.12214265887349</v>
-      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -19085,18 +16149,6 @@
       <c r="T245" t="n">
         <v>12</v>
       </c>
-      <c r="U245" t="n">
-        <v>3.869153819594704</v>
-      </c>
-      <c r="V245" t="n">
-        <v>10.83303126593456</v>
-      </c>
-      <c r="W245" t="n">
-        <v>3.867269440247691</v>
-      </c>
-      <c r="X245" t="n">
-        <v>10.88439633338454</v>
-      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -19161,18 +16213,6 @@
       <c r="T246" t="n">
         <v>12</v>
       </c>
-      <c r="U246" t="n">
-        <v>3.914077176160009</v>
-      </c>
-      <c r="V246" t="n">
-        <v>15.27620914059569</v>
-      </c>
-      <c r="W246" t="n">
-        <v>3.897873132725703</v>
-      </c>
-      <c r="X246" t="n">
-        <v>15.19217807754997</v>
-      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -19237,18 +16277,6 @@
       <c r="T247" t="n">
         <v>12</v>
       </c>
-      <c r="U247" t="n">
-        <v>3.792761733292332</v>
-      </c>
-      <c r="V247" t="n">
-        <v>10.75095268177821</v>
-      </c>
-      <c r="W247" t="n">
-        <v>3.864284476941702</v>
-      </c>
-      <c r="X247" t="n">
-        <v>11.20213950012233</v>
-      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -19313,18 +16341,6 @@
       <c r="T248" t="n">
         <v>12</v>
       </c>
-      <c r="U248" t="n">
-        <v>3.937550481548089</v>
-      </c>
-      <c r="V248" t="n">
-        <v>16.11558867958871</v>
-      </c>
-      <c r="W248" t="n">
-        <v>3.966810325006642</v>
-      </c>
-      <c r="X248" t="n">
-        <v>16.44081506638707</v>
-      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -19389,18 +16405,6 @@
       <c r="T249" t="n">
         <v>12</v>
       </c>
-      <c r="U249" t="n">
-        <v>0.4997954537157088</v>
-      </c>
-      <c r="V249" t="n">
-        <v>20.49208805315078</v>
-      </c>
-      <c r="W249" t="n">
-        <v>0.4998161851711451</v>
-      </c>
-      <c r="X249" t="n">
-        <v>21.61861512157029</v>
-      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -19465,18 +16469,6 @@
       <c r="T250" t="n">
         <v>11</v>
       </c>
-      <c r="U250" t="n">
-        <v>0.4998506504408217</v>
-      </c>
-      <c r="V250" t="n">
-        <v>27.93120253669603</v>
-      </c>
-      <c r="W250" t="n">
-        <v>0.4998729944317691</v>
-      </c>
-      <c r="X250" t="n">
-        <v>28.39859886994067</v>
-      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -19541,18 +16533,6 @@
       <c r="T251" t="n">
         <v>11</v>
       </c>
-      <c r="U251" t="n">
-        <v>0.4995273793857037</v>
-      </c>
-      <c r="V251" t="n">
-        <v>25.81844239943381</v>
-      </c>
-      <c r="W251" t="n">
-        <v>0.4994924761026558</v>
-      </c>
-      <c r="X251" t="n">
-        <v>25.94366785276336</v>
-      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -19617,18 +16597,6 @@
       <c r="T252" t="n">
         <v>11</v>
       </c>
-      <c r="U252" t="n">
-        <v>0.4997671564398986</v>
-      </c>
-      <c r="V252" t="n">
-        <v>25.27780524773521</v>
-      </c>
-      <c r="W252" t="n">
-        <v>0.4997279558294796</v>
-      </c>
-      <c r="X252" t="n">
-        <v>25.4203459881964</v>
-      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -19693,18 +16661,6 @@
       <c r="T253" t="n">
         <v>11</v>
       </c>
-      <c r="U253" t="n">
-        <v>0.4994855886500599</v>
-      </c>
-      <c r="V253" t="n">
-        <v>19.8284203026161</v>
-      </c>
-      <c r="W253" t="n">
-        <v>0.4994374318689009</v>
-      </c>
-      <c r="X253" t="n">
-        <v>21.05196132746706</v>
-      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -19769,18 +16725,6 @@
       <c r="T254" t="n">
         <v>11</v>
       </c>
-      <c r="U254" t="n">
-        <v>0.4996857377555946</v>
-      </c>
-      <c r="V254" t="n">
-        <v>18.90229482078594</v>
-      </c>
-      <c r="W254" t="n">
-        <v>0.4996635948732657</v>
-      </c>
-      <c r="X254" t="n">
-        <v>18.81592089534288</v>
-      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -19845,18 +16789,6 @@
       <c r="T255" t="n">
         <v>11</v>
       </c>
-      <c r="U255" t="n">
-        <v>2.021425994144939</v>
-      </c>
-      <c r="V255" t="n">
-        <v>28.1084350686234</v>
-      </c>
-      <c r="W255" t="n">
-        <v>0.4996407893574041</v>
-      </c>
-      <c r="X255" t="n">
-        <v>16.05618854384624</v>
-      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -19921,18 +16853,6 @@
       <c r="T256" t="n">
         <v>11</v>
       </c>
-      <c r="U256" t="n">
-        <v>2.024319865666239</v>
-      </c>
-      <c r="V256" t="n">
-        <v>4.782102195986358</v>
-      </c>
-      <c r="W256" t="n">
-        <v>2.028827336131811</v>
-      </c>
-      <c r="X256" t="n">
-        <v>4.739978415893499</v>
-      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -19997,18 +16917,6 @@
       <c r="T257" t="n">
         <v>11</v>
       </c>
-      <c r="U257" t="n">
-        <v>2.008858568498134</v>
-      </c>
-      <c r="V257" t="n">
-        <v>27.40586330898038</v>
-      </c>
-      <c r="W257" t="n">
-        <v>2.011733351886994</v>
-      </c>
-      <c r="X257" t="n">
-        <v>4.871994513137498</v>
-      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -20073,18 +16981,6 @@
       <c r="T258" t="n">
         <v>11</v>
       </c>
-      <c r="U258" t="n">
-        <v>2.013912116063426</v>
-      </c>
-      <c r="V258" t="n">
-        <v>4.810167897018978</v>
-      </c>
-      <c r="W258" t="n">
-        <v>2.012046846115728</v>
-      </c>
-      <c r="X258" t="n">
-        <v>4.798304591438128</v>
-      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -20149,18 +17045,6 @@
       <c r="T259" t="n">
         <v>11</v>
       </c>
-      <c r="U259" t="n">
-        <v>2.007928164345357</v>
-      </c>
-      <c r="V259" t="n">
-        <v>4.799751561844157</v>
-      </c>
-      <c r="W259" t="n">
-        <v>0.4998675301853598</v>
-      </c>
-      <c r="X259" t="n">
-        <v>18.52411352883971</v>
-      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -20225,18 +17109,6 @@
       <c r="T260" t="n">
         <v>11</v>
       </c>
-      <c r="U260" t="n">
-        <v>2.012589581506131</v>
-      </c>
-      <c r="V260" t="n">
-        <v>4.735248719182505</v>
-      </c>
-      <c r="W260" t="n">
-        <v>0.4998126207533912</v>
-      </c>
-      <c r="X260" t="n">
-        <v>22.74993611378078</v>
-      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -20301,18 +17173,6 @@
       <c r="T261" t="n">
         <v>11</v>
       </c>
-      <c r="U261" t="n">
-        <v>2.008392466476194</v>
-      </c>
-      <c r="V261" t="n">
-        <v>4.808773531310317</v>
-      </c>
-      <c r="W261" t="n">
-        <v>0.4998625364404873</v>
-      </c>
-      <c r="X261" t="n">
-        <v>19.71852440671987</v>
-      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -20377,18 +17237,6 @@
       <c r="T262" t="n">
         <v>11</v>
       </c>
-      <c r="U262" t="n">
-        <v>0.500186703416987</v>
-      </c>
-      <c r="V262" t="n">
-        <v>15.97669343587651</v>
-      </c>
-      <c r="W262" t="n">
-        <v>0.500232464365393</v>
-      </c>
-      <c r="X262" t="n">
-        <v>15.29596537510095</v>
-      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -20453,18 +17301,6 @@
       <c r="T263" t="n">
         <v>11</v>
       </c>
-      <c r="U263" t="n">
-        <v>0.4997625956595536</v>
-      </c>
-      <c r="V263" t="n">
-        <v>29.98164355839377</v>
-      </c>
-      <c r="W263" t="n">
-        <v>0.5014015271793043</v>
-      </c>
-      <c r="X263" t="n">
-        <v>3.596668755931962</v>
-      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -20529,18 +17365,6 @@
       <c r="T264" t="n">
         <v>11</v>
       </c>
-      <c r="U264" t="n">
-        <v>0.5000516129344305</v>
-      </c>
-      <c r="V264" t="n">
-        <v>27.84919607523602</v>
-      </c>
-      <c r="W264" t="n">
-        <v>0.5002067182953592</v>
-      </c>
-      <c r="X264" t="n">
-        <v>25.78090140107033</v>
-      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -20605,18 +17429,6 @@
       <c r="T265" t="n">
         <v>11</v>
       </c>
-      <c r="U265" t="n">
-        <v>0.4998425723249651</v>
-      </c>
-      <c r="V265" t="n">
-        <v>23.42630303762351</v>
-      </c>
-      <c r="W265" t="n">
-        <v>1.995140934540166</v>
-      </c>
-      <c r="X265" t="n">
-        <v>4.535722645001605</v>
-      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -20681,18 +17493,6 @@
       <c r="T266" t="n">
         <v>11</v>
       </c>
-      <c r="U266" t="n">
-        <v>0.5001654781213548</v>
-      </c>
-      <c r="V266" t="n">
-        <v>30.51945796159189</v>
-      </c>
-      <c r="W266" t="n">
-        <v>0.5000523743062218</v>
-      </c>
-      <c r="X266" t="n">
-        <v>31.39363420903871</v>
-      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -20757,18 +17557,6 @@
       <c r="T267" t="n">
         <v>11</v>
       </c>
-      <c r="U267" t="n">
-        <v>0.5004794857112586</v>
-      </c>
-      <c r="V267" t="n">
-        <v>17.66123981460083</v>
-      </c>
-      <c r="W267" t="n">
-        <v>0.500576428746732</v>
-      </c>
-      <c r="X267" t="n">
-        <v>17.10963401117375</v>
-      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -20833,18 +17621,6 @@
       <c r="T268" t="n">
         <v>10</v>
       </c>
-      <c r="U268" t="n">
-        <v>0.4984494217294435</v>
-      </c>
-      <c r="V268" t="n">
-        <v>6.947991925041814</v>
-      </c>
-      <c r="W268" t="n">
-        <v>0.4982725041082089</v>
-      </c>
-      <c r="X268" t="n">
-        <v>7.025740180834569</v>
-      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -20909,18 +17685,6 @@
       <c r="T269" t="n">
         <v>10</v>
       </c>
-      <c r="U269" t="n">
-        <v>0.499284855346903</v>
-      </c>
-      <c r="V269" t="n">
-        <v>5.733078032829286</v>
-      </c>
-      <c r="W269" t="n">
-        <v>0.4990826377633884</v>
-      </c>
-      <c r="X269" t="n">
-        <v>6.046243397501521</v>
-      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -20985,18 +17749,6 @@
       <c r="T270" t="n">
         <v>11</v>
       </c>
-      <c r="U270" t="n">
-        <v>0.4994710862510632</v>
-      </c>
-      <c r="V270" t="n">
-        <v>5.677896665220326</v>
-      </c>
-      <c r="W270" t="n">
-        <v>0.4996345820106984</v>
-      </c>
-      <c r="X270" t="n">
-        <v>6.193620889087237</v>
-      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -21061,18 +17813,6 @@
       <c r="T271" t="n">
         <v>11</v>
       </c>
-      <c r="U271" t="n">
-        <v>0.4997533381077705</v>
-      </c>
-      <c r="V271" t="n">
-        <v>7.314901468444832</v>
-      </c>
-      <c r="W271" t="n">
-        <v>0.4995875625801832</v>
-      </c>
-      <c r="X271" t="n">
-        <v>7.26346207777576</v>
-      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -21137,18 +17877,6 @@
       <c r="T272" t="n">
         <v>11</v>
       </c>
-      <c r="U272" t="n">
-        <v>0.5002465186131709</v>
-      </c>
-      <c r="V272" t="n">
-        <v>7.037115105789733</v>
-      </c>
-      <c r="W272" t="n">
-        <v>0.4998949365792965</v>
-      </c>
-      <c r="X272" t="n">
-        <v>6.951320816604379</v>
-      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -21213,18 +17941,6 @@
       <c r="T273" t="n">
         <v>11</v>
       </c>
-      <c r="U273" t="n">
-        <v>0.4996993236768517</v>
-      </c>
-      <c r="V273" t="n">
-        <v>9.66082011864852</v>
-      </c>
-      <c r="W273" t="n">
-        <v>0.499761049740893</v>
-      </c>
-      <c r="X273" t="n">
-        <v>9.325433278528786</v>
-      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -21289,18 +18005,6 @@
       <c r="T274" t="n">
         <v>11</v>
       </c>
-      <c r="U274" t="n">
-        <v>1.985054866613851</v>
-      </c>
-      <c r="V274" t="n">
-        <v>5.08892850124766</v>
-      </c>
-      <c r="W274" t="n">
-        <v>1.98686405368529</v>
-      </c>
-      <c r="X274" t="n">
-        <v>5.094343133450727</v>
-      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -21365,18 +18069,6 @@
       <c r="T275" t="n">
         <v>11</v>
       </c>
-      <c r="U275" t="n">
-        <v>0.4995691916114058</v>
-      </c>
-      <c r="V275" t="n">
-        <v>11.57009430695143</v>
-      </c>
-      <c r="W275" t="n">
-        <v>0.4995309342618738</v>
-      </c>
-      <c r="X275" t="n">
-        <v>10.98489871157228</v>
-      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -21441,18 +18133,6 @@
       <c r="T276" t="n">
         <v>11</v>
       </c>
-      <c r="U276" t="n">
-        <v>0.4984920091638732</v>
-      </c>
-      <c r="V276" t="n">
-        <v>9.041276032636382</v>
-      </c>
-      <c r="W276" t="n">
-        <v>0.4976516980137621</v>
-      </c>
-      <c r="X276" t="n">
-        <v>7.92795399115024</v>
-      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -21517,18 +18197,6 @@
       <c r="T277" t="n">
         <v>11</v>
       </c>
-      <c r="U277" t="n">
-        <v>0.5005986970820967</v>
-      </c>
-      <c r="V277" t="n">
-        <v>26.1797645837691</v>
-      </c>
-      <c r="W277" t="n">
-        <v>0.5006848161991692</v>
-      </c>
-      <c r="X277" t="n">
-        <v>25.74721656209233</v>
-      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -21593,18 +18261,6 @@
       <c r="T278" t="n">
         <v>11</v>
       </c>
-      <c r="U278" t="n">
-        <v>0.4982120215464519</v>
-      </c>
-      <c r="V278" t="n">
-        <v>5.340934438919681</v>
-      </c>
-      <c r="W278" t="n">
-        <v>0.4977868567737637</v>
-      </c>
-      <c r="X278" t="n">
-        <v>5.577887913262511</v>
-      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -21669,18 +18325,6 @@
       <c r="T279" t="n">
         <v>11</v>
       </c>
-      <c r="U279" t="n">
-        <v>0.5005597525151138</v>
-      </c>
-      <c r="V279" t="n">
-        <v>5.887788503524925</v>
-      </c>
-      <c r="W279" t="n">
-        <v>0.5008005964131156</v>
-      </c>
-      <c r="X279" t="n">
-        <v>5.933126045243382</v>
-      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -21745,18 +18389,6 @@
       <c r="T280" t="n">
         <v>11</v>
       </c>
-      <c r="U280" t="n">
-        <v>0.5007793589805282</v>
-      </c>
-      <c r="V280" t="n">
-        <v>34.62615780973638</v>
-      </c>
-      <c r="W280" t="n">
-        <v>0.5012815740777091</v>
-      </c>
-      <c r="X280" t="n">
-        <v>35.58953598139695</v>
-      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -21821,18 +18453,6 @@
       <c r="T281" t="n">
         <v>11</v>
       </c>
-      <c r="U281" t="n">
-        <v>0.5003717740696462</v>
-      </c>
-      <c r="V281" t="n">
-        <v>4.731113928416778</v>
-      </c>
-      <c r="W281" t="n">
-        <v>0.5024171962452308</v>
-      </c>
-      <c r="X281" t="n">
-        <v>4.931584715675152</v>
-      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -21897,18 +18517,6 @@
       <c r="T282" t="n">
         <v>11</v>
       </c>
-      <c r="U282" t="n">
-        <v>5.458346119202902</v>
-      </c>
-      <c r="V282" t="n">
-        <v>25.06916678432665</v>
-      </c>
-      <c r="W282" t="n">
-        <v>5.213713080959437</v>
-      </c>
-      <c r="X282" t="n">
-        <v>23.42612180227705</v>
-      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -21973,18 +18581,6 @@
       <c r="T283" t="n">
         <v>11</v>
       </c>
-      <c r="U283" t="n">
-        <v>6.00537095760976</v>
-      </c>
-      <c r="V283" t="n">
-        <v>29.02940819203739</v>
-      </c>
-      <c r="W283" t="n">
-        <v>1.989376735991938</v>
-      </c>
-      <c r="X283" t="n">
-        <v>4.656701571828295</v>
-      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -22049,18 +18645,6 @@
       <c r="T284" t="n">
         <v>11</v>
       </c>
-      <c r="U284" t="n">
-        <v>0.5005153403213913</v>
-      </c>
-      <c r="V284" t="n">
-        <v>5.004261711624898</v>
-      </c>
-      <c r="W284" t="n">
-        <v>0.500823963795911</v>
-      </c>
-      <c r="X284" t="n">
-        <v>5.065712337636344</v>
-      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -22125,18 +18709,6 @@
       <c r="T285" t="n">
         <v>10</v>
       </c>
-      <c r="U285" t="n">
-        <v>4.622895705755446</v>
-      </c>
-      <c r="V285" t="n">
-        <v>49.94050090463998</v>
-      </c>
-      <c r="W285" t="n">
-        <v>4.595739263295424</v>
-      </c>
-      <c r="X285" t="n">
-        <v>19.9451328140103</v>
-      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -22201,18 +18773,6 @@
       <c r="T286" t="n">
         <v>10</v>
       </c>
-      <c r="U286" t="n">
-        <v>4.855085108418066</v>
-      </c>
-      <c r="V286" t="n">
-        <v>14.05827495272711</v>
-      </c>
-      <c r="W286" t="n">
-        <v>4.723281592967463</v>
-      </c>
-      <c r="X286" t="n">
-        <v>18.67459358995252</v>
-      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -22277,18 +18837,6 @@
       <c r="T287" t="n">
         <v>10</v>
       </c>
-      <c r="U287" t="n">
-        <v>3.999893435832682</v>
-      </c>
-      <c r="V287" t="n">
-        <v>9.575141906046474</v>
-      </c>
-      <c r="W287" t="n">
-        <v>4.104669299419796</v>
-      </c>
-      <c r="X287" t="n">
-        <v>9.190226157146068</v>
-      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -22353,18 +18901,6 @@
       <c r="T288" t="n">
         <v>10</v>
       </c>
-      <c r="U288" t="n">
-        <v>3.36518300717964</v>
-      </c>
-      <c r="V288" t="n">
-        <v>7.819113782430952</v>
-      </c>
-      <c r="W288" t="n">
-        <v>3.23349683901652</v>
-      </c>
-      <c r="X288" t="n">
-        <v>8.011438314378225</v>
-      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -22429,18 +18965,6 @@
       <c r="T289" t="n">
         <v>10</v>
       </c>
-      <c r="U289" t="n">
-        <v>0.4976680565993663</v>
-      </c>
-      <c r="V289" t="n">
-        <v>16.51517140099631</v>
-      </c>
-      <c r="W289" t="n">
-        <v>0.4971424954260566</v>
-      </c>
-      <c r="X289" t="n">
-        <v>15.69432890497389</v>
-      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -22505,18 +19029,6 @@
       <c r="T290" t="n">
         <v>10</v>
       </c>
-      <c r="U290" t="n">
-        <v>0.4964344162556237</v>
-      </c>
-      <c r="V290" t="n">
-        <v>15.09851904463349</v>
-      </c>
-      <c r="W290" t="n">
-        <v>0.4955729697443423</v>
-      </c>
-      <c r="X290" t="n">
-        <v>14.07229262203902</v>
-      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -22581,18 +19093,6 @@
       <c r="T291" t="n">
         <v>11</v>
       </c>
-      <c r="U291" t="n">
-        <v>3.144501386702052</v>
-      </c>
-      <c r="V291" t="n">
-        <v>7.065125098467315</v>
-      </c>
-      <c r="W291" t="n">
-        <v>3.030048336744425</v>
-      </c>
-      <c r="X291" t="n">
-        <v>7.962497260839993</v>
-      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -22657,18 +19157,6 @@
       <c r="T292" t="n">
         <v>11</v>
       </c>
-      <c r="U292" t="n">
-        <v>2.7915991118982</v>
-      </c>
-      <c r="V292" t="n">
-        <v>5.203713993508823</v>
-      </c>
-      <c r="W292" t="n">
-        <v>3.153186170987109</v>
-      </c>
-      <c r="X292" t="n">
-        <v>6.915216264286341</v>
-      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -22733,18 +19221,6 @@
       <c r="T293" t="n">
         <v>11</v>
       </c>
-      <c r="U293" t="n">
-        <v>3.449196097039882</v>
-      </c>
-      <c r="V293" t="n">
-        <v>8.086100617570251</v>
-      </c>
-      <c r="W293" t="n">
-        <v>3.312896051413294</v>
-      </c>
-      <c r="X293" t="n">
-        <v>7.45742863950295</v>
-      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -22809,18 +19285,6 @@
       <c r="T294" t="n">
         <v>11</v>
       </c>
-      <c r="U294" t="n">
-        <v>3.054179943053131</v>
-      </c>
-      <c r="V294" t="n">
-        <v>6.432604184736494</v>
-      </c>
-      <c r="W294" t="n">
-        <v>2.94489238644835</v>
-      </c>
-      <c r="X294" t="n">
-        <v>5.923130674514509</v>
-      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -22885,18 +19349,6 @@
       <c r="T295" t="n">
         <v>11</v>
       </c>
-      <c r="U295" t="n">
-        <v>2.896289729972495</v>
-      </c>
-      <c r="V295" t="n">
-        <v>5.304738852062403</v>
-      </c>
-      <c r="W295" t="n">
-        <v>2.805576471938133</v>
-      </c>
-      <c r="X295" t="n">
-        <v>5.162179269880349</v>
-      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -22961,18 +19413,6 @@
       <c r="T296" t="n">
         <v>11</v>
       </c>
-      <c r="U296" t="n">
-        <v>1.841544039779958</v>
-      </c>
-      <c r="V296" t="n">
-        <v>26.95400901460415</v>
-      </c>
-      <c r="W296" t="n">
-        <v>2.531098459361275</v>
-      </c>
-      <c r="X296" t="n">
-        <v>4.844900652612639</v>
-      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -23037,18 +19477,6 @@
       <c r="T297" t="n">
         <v>11</v>
       </c>
-      <c r="U297" t="n">
-        <v>1.665491043010531</v>
-      </c>
-      <c r="V297" t="n">
-        <v>21.36563209345869</v>
-      </c>
-      <c r="W297" t="n">
-        <v>1.609346009878101</v>
-      </c>
-      <c r="X297" t="n">
-        <v>16.66565435719357</v>
-      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -23113,18 +19541,6 @@
       <c r="T298" t="n">
         <v>11</v>
       </c>
-      <c r="U298" t="n">
-        <v>1.79892204869728</v>
-      </c>
-      <c r="V298" t="n">
-        <v>4.733451187521103</v>
-      </c>
-      <c r="W298" t="n">
-        <v>1.689727801655303</v>
-      </c>
-      <c r="X298" t="n">
-        <v>19.53366253189965</v>
-      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -23189,18 +19605,6 @@
       <c r="T299" t="n">
         <v>11</v>
       </c>
-      <c r="U299" t="n">
-        <v>1.664989254830909</v>
-      </c>
-      <c r="V299" t="n">
-        <v>22.26126329694353</v>
-      </c>
-      <c r="W299" t="n">
-        <v>4.943388863994994</v>
-      </c>
-      <c r="X299" t="n">
-        <v>2.169262677927067</v>
-      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -23265,18 +19669,6 @@
       <c r="T300" t="n">
         <v>11</v>
       </c>
-      <c r="U300" t="n">
-        <v>0.4998545648475067</v>
-      </c>
-      <c r="V300" t="n">
-        <v>21.67512531829881</v>
-      </c>
-      <c r="W300" t="n">
-        <v>0.4989101910445144</v>
-      </c>
-      <c r="X300" t="n">
-        <v>23.09681125502046</v>
-      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -23341,18 +19733,6 @@
       <c r="T301" t="n">
         <v>11</v>
       </c>
-      <c r="U301" t="n">
-        <v>1.905715601540251</v>
-      </c>
-      <c r="V301" t="n">
-        <v>24.88005905423724</v>
-      </c>
-      <c r="W301" t="n">
-        <v>1.900914832021262</v>
-      </c>
-      <c r="X301" t="n">
-        <v>14.82163399957617</v>
-      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -23417,18 +19797,6 @@
       <c r="T302" t="n">
         <v>11</v>
       </c>
-      <c r="U302" t="n">
-        <v>0.4999194198789848</v>
-      </c>
-      <c r="V302" t="n">
-        <v>15.39803189330929</v>
-      </c>
-      <c r="W302" t="n">
-        <v>1.959747344978822</v>
-      </c>
-      <c r="X302" t="n">
-        <v>28.40454792664166</v>
-      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -23493,18 +19861,6 @@
       <c r="T303" t="n">
         <v>10</v>
       </c>
-      <c r="U303" t="n">
-        <v>3.230761490521761</v>
-      </c>
-      <c r="V303" t="n">
-        <v>5.42428574842054</v>
-      </c>
-      <c r="W303" t="n">
-        <v>3.156486055126338</v>
-      </c>
-      <c r="X303" t="n">
-        <v>5.350134956549735</v>
-      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -23569,18 +19925,6 @@
       <c r="T304" t="n">
         <v>10</v>
       </c>
-      <c r="U304" t="n">
-        <v>3.542470315552138</v>
-      </c>
-      <c r="V304" t="n">
-        <v>5.40983090275991</v>
-      </c>
-      <c r="W304" t="n">
-        <v>3.496155933389732</v>
-      </c>
-      <c r="X304" t="n">
-        <v>5.427244981938813</v>
-      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -23645,18 +19989,6 @@
       <c r="T305" t="n">
         <v>10</v>
       </c>
-      <c r="U305" t="n">
-        <v>2.91145890547362</v>
-      </c>
-      <c r="V305" t="n">
-        <v>5.301572385992833</v>
-      </c>
-      <c r="W305" t="n">
-        <v>2.80645891784736</v>
-      </c>
-      <c r="X305" t="n">
-        <v>5.112550580498239</v>
-      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -23721,18 +20053,6 @@
       <c r="T306" t="n">
         <v>10</v>
       </c>
-      <c r="U306" t="n">
-        <v>1.914710596678444</v>
-      </c>
-      <c r="V306" t="n">
-        <v>24.75812111220269</v>
-      </c>
-      <c r="W306" t="n">
-        <v>2.925838044867239</v>
-      </c>
-      <c r="X306" t="n">
-        <v>5.25853945642621</v>
-      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -23797,18 +20117,6 @@
       <c r="T307" t="n">
         <v>11</v>
       </c>
-      <c r="U307" t="n">
-        <v>1.954176607875598</v>
-      </c>
-      <c r="V307" t="n">
-        <v>9.675671504856325</v>
-      </c>
-      <c r="W307" t="n">
-        <v>1.934851932883191</v>
-      </c>
-      <c r="X307" t="n">
-        <v>14.17429296752103</v>
-      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -23873,18 +20181,6 @@
       <c r="T308" t="n">
         <v>11</v>
       </c>
-      <c r="U308" t="n">
-        <v>8.542572853098978</v>
-      </c>
-      <c r="V308" t="n">
-        <v>4.368619034386141</v>
-      </c>
-      <c r="W308" t="n">
-        <v>4.471178733189314</v>
-      </c>
-      <c r="X308" t="n">
-        <v>9.691227636115796</v>
-      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -23949,18 +20245,6 @@
       <c r="T309" t="n">
         <v>11</v>
       </c>
-      <c r="U309" t="n">
-        <v>3.231699584907664</v>
-      </c>
-      <c r="V309" t="n">
-        <v>5.657507014393986</v>
-      </c>
-      <c r="W309" t="n">
-        <v>3.161100726325389</v>
-      </c>
-      <c r="X309" t="n">
-        <v>5.588494978633125</v>
-      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -24025,18 +20309,6 @@
       <c r="T310" t="n">
         <v>11</v>
       </c>
-      <c r="U310" t="n">
-        <v>3.526931321684846</v>
-      </c>
-      <c r="V310" t="n">
-        <v>5.728900588428425</v>
-      </c>
-      <c r="W310" t="n">
-        <v>3.483057226468486</v>
-      </c>
-      <c r="X310" t="n">
-        <v>5.759982975283645</v>
-      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -24101,18 +20373,6 @@
       <c r="T311" t="n">
         <v>11</v>
       </c>
-      <c r="U311" t="n">
-        <v>5.245414505785143</v>
-      </c>
-      <c r="V311" t="n">
-        <v>11.62855122504621</v>
-      </c>
-      <c r="W311" t="n">
-        <v>5.225853922278626</v>
-      </c>
-      <c r="X311" t="n">
-        <v>13.37873653314614</v>
-      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -24177,18 +20437,6 @@
       <c r="T312" t="n">
         <v>11</v>
       </c>
-      <c r="U312" t="n">
-        <v>6.448860169422388</v>
-      </c>
-      <c r="V312" t="n">
-        <v>12.77003194766257</v>
-      </c>
-      <c r="W312" t="n">
-        <v>6.201425242070083</v>
-      </c>
-      <c r="X312" t="n">
-        <v>12.44504075908926</v>
-      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -24253,18 +20501,6 @@
       <c r="T313" t="n">
         <v>12</v>
       </c>
-      <c r="U313" t="n">
-        <v>3.38453689054508</v>
-      </c>
-      <c r="V313" t="n">
-        <v>5.5570440770673</v>
-      </c>
-      <c r="W313" t="n">
-        <v>3.323742055839895</v>
-      </c>
-      <c r="X313" t="n">
-        <v>5.509755432634364</v>
-      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -24328,18 +20564,6 @@
       </c>
       <c r="T314" t="n">
         <v>12</v>
-      </c>
-      <c r="U314" t="n">
-        <v>0.4997841384891557</v>
-      </c>
-      <c r="V314" t="n">
-        <v>13.04183167806398</v>
-      </c>
-      <c r="W314" t="n">
-        <v>0.4996888315474082</v>
-      </c>
-      <c r="X314" t="n">
-        <v>12.88797368787679</v>
       </c>
     </row>
   </sheetData>
